--- a/ferndata.xlsx
+++ b/ferndata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sallyborrowman/data_science/EEPferns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4F3936F-5F98-4C45-8635-A58AF9B4DCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0211F44-FAE2-8640-868A-AE36AA3DFB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="17280" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="17240" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="60">
   <si>
-    <t xml:space="preserve">Running order </t>
-  </si>
-  <si>
     <t>Recorder</t>
   </si>
   <si>
@@ -63,24 +60,6 @@
   </si>
   <si>
     <t>Species</t>
-  </si>
-  <si>
-    <t>Length of longest frond (mm)</t>
-  </si>
-  <si>
-    <t>Number of fronds</t>
-  </si>
-  <si>
-    <t>Number of fertile fronds</t>
-  </si>
-  <si>
-    <t>Length of Blade (mm)</t>
-  </si>
-  <si>
-    <t>Stipe length of tallest leaf (mm)</t>
-  </si>
-  <si>
-    <t>Width of blade (at widest) (mm)</t>
   </si>
   <si>
     <t>Naomi</t>
@@ -216,6 +195,27 @@
   </si>
   <si>
     <t>Arthur's Seat</t>
+  </si>
+  <si>
+    <t>ftondlength</t>
+  </si>
+  <si>
+    <t>numberfrond</t>
+  </si>
+  <si>
+    <t>fertilefrond</t>
+  </si>
+  <si>
+    <t>bladelength</t>
+  </si>
+  <si>
+    <t>runningorder</t>
+  </si>
+  <si>
+    <t>stipelength</t>
+  </si>
+  <si>
+    <t>bladewidth</t>
   </si>
 </sst>
 </file>
@@ -658,51 +658,51 @@
     <col min="9" max="9" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5">
         <v>46144</v>
@@ -722,16 +722,16 @@
         <v>-3.17517</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4">
         <v>80</v>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5">
         <v>46144</v>
@@ -769,16 +769,16 @@
         <v>-3.17517</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J3" s="4">
         <v>27</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5">
         <v>46236</v>
@@ -816,16 +816,16 @@
         <v>-3.18276</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4">
         <v>58</v>
@@ -851,7 +851,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5">
         <v>46236</v>
@@ -863,16 +863,16 @@
         <v>-3.18276</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J5" s="4">
         <v>90</v>
@@ -898,7 +898,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6" s="5">
         <v>46236</v>
@@ -910,16 +910,16 @@
         <v>-3.1893500000000001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J6" s="4">
         <v>36</v>
@@ -945,7 +945,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5">
         <v>46236</v>
@@ -957,16 +957,16 @@
         <v>-3.1897199999999999</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J7" s="4">
         <v>61</v>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5">
         <v>46236</v>
@@ -1004,16 +1004,16 @@
         <v>-3.1897199999999999</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J8" s="4">
         <v>58</v>
@@ -1039,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5">
         <v>46236</v>
@@ -1051,16 +1051,16 @@
         <v>-3.1928100000000001</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4">
         <v>45</v>
@@ -1086,7 +1086,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5">
         <v>46236</v>
@@ -1098,16 +1098,16 @@
         <v>-3.1928100000000001</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J10" s="4">
         <v>85</v>
@@ -1133,7 +1133,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5">
         <v>46236</v>
@@ -1145,16 +1145,16 @@
         <v>-3.1931699999999998</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J11" s="4">
         <v>115</v>
@@ -1180,7 +1180,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5">
         <v>46236</v>
@@ -1192,16 +1192,16 @@
         <v>-3.1931699999999998</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J12" s="4">
         <v>42</v>
@@ -1227,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5">
         <v>46236</v>
@@ -1239,16 +1239,16 @@
         <v>-3.1933699999999998</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4">
         <v>193</v>
@@ -1274,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5">
         <v>46236</v>
@@ -1286,16 +1286,16 @@
         <v>-3.1933699999999998</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J14" s="4">
         <v>92</v>
@@ -1321,7 +1321,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C15" s="5">
         <v>46236</v>
@@ -1333,16 +1333,16 @@
         <v>-3.1938200000000001</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J15" s="4">
         <v>12</v>
@@ -1368,7 +1368,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C16" s="5">
         <v>46236</v>
@@ -1380,16 +1380,16 @@
         <v>-3.1938200000000001</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4">
         <v>56</v>
@@ -1415,7 +1415,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C17" s="5">
         <v>46236</v>
@@ -1427,16 +1427,16 @@
         <v>-3.1926999999999999</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J17" s="4">
         <v>65</v>
@@ -1462,7 +1462,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C18" s="5">
         <v>46236</v>
@@ -1474,16 +1474,16 @@
         <v>-3.1926999999999999</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J18" s="4">
         <v>107</v>
@@ -1509,7 +1509,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C19" s="5">
         <v>46236</v>
@@ -1521,16 +1521,16 @@
         <v>-3.1913900000000002</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J19" s="4">
         <v>151</v>
@@ -1556,7 +1556,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C20" s="5">
         <v>46236</v>
@@ -1568,16 +1568,16 @@
         <v>-3.1912699999999998</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J20" s="4">
         <v>95</v>
@@ -1603,7 +1603,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C21" s="5">
         <v>46236</v>
@@ -1615,16 +1615,16 @@
         <v>-3.1912699999999998</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4">
         <v>19</v>
@@ -1650,7 +1650,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C22" s="5">
         <v>46236</v>
@@ -1662,16 +1662,16 @@
         <v>-3.1911800000000001</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J22" s="4">
         <v>121</v>
@@ -1697,7 +1697,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C23" s="5">
         <v>46236</v>
@@ -1709,16 +1709,16 @@
         <v>-3.1908300000000001</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="J23" s="4">
         <v>89</v>
@@ -1744,7 +1744,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C24" s="5">
         <v>46205</v>
@@ -1756,16 +1756,16 @@
         <v>-3.1641900000000001</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J24" s="4">
         <v>540</v>
@@ -1791,7 +1791,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C25" s="5">
         <v>46205</v>
@@ -1803,16 +1803,16 @@
         <v>-3.1642800000000002</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J25" s="4">
         <v>610</v>
@@ -1838,7 +1838,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C26" s="5">
         <v>46205</v>
@@ -1850,16 +1850,16 @@
         <v>-3.1651199999999999</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J26" s="4">
         <v>205</v>
@@ -1885,7 +1885,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C27" s="5">
         <v>46205</v>
@@ -1897,16 +1897,16 @@
         <v>-3.1652800000000001</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J27" s="4">
         <v>200</v>
@@ -1932,7 +1932,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C28" s="5">
         <v>46205</v>
@@ -1944,16 +1944,16 @@
         <v>-3.16736</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4">
         <v>580</v>
@@ -1979,7 +1979,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C29" s="5">
         <v>46060</v>
@@ -1991,16 +1991,16 @@
         <v>-3.1672600000000002</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J29" s="4">
         <v>800</v>
@@ -2026,7 +2026,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C30" s="5">
         <v>46065</v>
@@ -2038,16 +2038,16 @@
         <v>-3.1930000000000001</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4">
         <v>110</v>
@@ -2073,7 +2073,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" s="5">
         <v>46065</v>
@@ -2085,16 +2085,16 @@
         <v>-3.1931799999999999</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J31" s="4">
         <v>126</v>
@@ -2120,7 +2120,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C32" s="5">
         <v>46065</v>
@@ -2132,16 +2132,16 @@
         <v>-3.1942699999999999</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J32" s="4">
         <v>498</v>
@@ -2167,7 +2167,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C33" s="5">
         <v>46065</v>
@@ -2179,16 +2179,16 @@
         <v>-3.1945000000000001</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J33" s="4">
         <v>265</v>
@@ -2214,7 +2214,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C34" s="5">
         <v>46065</v>
@@ -2226,16 +2226,16 @@
         <v>-3.1955900000000002</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4">
         <v>110</v>
@@ -2261,7 +2261,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C35" s="5">
         <v>46065</v>
@@ -2273,16 +2273,16 @@
         <v>-3.1966800000000002</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J35" s="4">
         <v>121</v>
@@ -2308,7 +2308,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C36" s="5">
         <v>46065</v>
@@ -2320,16 +2320,16 @@
         <v>-3.1967699999999999</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J36" s="4">
         <v>148</v>
@@ -2355,7 +2355,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C37" s="5">
         <v>46065</v>
@@ -2367,16 +2367,16 @@
         <v>-3.1968200000000002</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J37" s="4">
         <v>177</v>
@@ -2402,7 +2402,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C38" s="5">
         <v>46065</v>
@@ -2414,16 +2414,16 @@
         <v>-3.19679</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J38" s="4">
         <v>135</v>
@@ -2449,7 +2449,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C39" s="5">
         <v>46065</v>
@@ -2461,16 +2461,16 @@
         <v>-3.1968999999999999</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J39" s="4">
         <v>174</v>
@@ -2496,7 +2496,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C40" s="5">
         <v>46065</v>
@@ -2508,16 +2508,16 @@
         <v>-3.19678</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J40" s="4">
         <v>267</v>
@@ -2543,7 +2543,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C41" s="5">
         <v>46065</v>
@@ -2555,16 +2555,16 @@
         <v>-3.1966299999999999</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J41" s="4">
         <v>109</v>
@@ -2590,7 +2590,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C42" s="5">
         <v>46065</v>
@@ -2602,16 +2602,16 @@
         <v>-3.1911100000000001</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J42" s="4">
         <v>870</v>
@@ -2637,7 +2637,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C43" s="5">
         <v>46065</v>
@@ -2649,16 +2649,16 @@
         <v>-3.1938399999999998</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J43" s="4">
         <v>42</v>
@@ -2684,7 +2684,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C44" s="5">
         <v>46065</v>
@@ -2696,16 +2696,16 @@
         <v>-3.1968299999999998</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J44" s="4">
         <v>34</v>
@@ -2731,7 +2731,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C45" s="5">
         <v>46065</v>
@@ -2743,16 +2743,16 @@
         <v>-3.1967400000000001</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J45" s="4">
         <v>22</v>
@@ -2778,7 +2778,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C46" s="5">
         <v>46065</v>
@@ -2790,16 +2790,16 @@
         <v>-3.1972800000000001</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J46" s="4">
         <v>28</v>
@@ -2825,7 +2825,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C47" s="5">
         <v>46065</v>
@@ -2837,16 +2837,16 @@
         <v>-3.1960799999999998</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J47" s="4">
         <v>6</v>
@@ -2872,7 +2872,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C48" s="5">
         <v>46358</v>
@@ -2884,16 +2884,16 @@
         <v>-3.1968100000000002</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J48" s="4">
         <v>20</v>
@@ -2919,7 +2919,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C49" s="5">
         <v>46065</v>
@@ -2931,16 +2931,16 @@
         <v>-3.19659</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4">
         <v>296</v>
@@ -2966,7 +2966,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C50" s="5">
         <v>46065</v>
@@ -2978,16 +2978,16 @@
         <v>-3.1957100000000001</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="J50" s="4">
         <v>153</v>
@@ -3013,7 +3013,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C51" s="5">
         <v>46358</v>
@@ -3025,16 +3025,16 @@
         <v>-3.1915200000000001</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J51" s="4">
         <v>550</v>
@@ -3060,7 +3060,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C52" s="5">
         <v>46065</v>
@@ -3072,16 +3072,16 @@
         <v>-3.1932</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J52" s="4">
         <v>190</v>
@@ -3107,7 +3107,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C53" s="5">
         <v>46065</v>
@@ -3119,16 +3119,16 @@
         <v>-3.1938200000000001</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J53" s="4">
         <v>495</v>
@@ -3154,7 +3154,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C54" s="5">
         <v>46065</v>
@@ -3166,16 +3166,16 @@
         <v>-3.1969099999999999</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J54" s="4">
         <v>94</v>
@@ -3201,7 +3201,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C55" s="5">
         <v>46065</v>
@@ -3213,16 +3213,16 @@
         <v>-3.1970700000000001</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J55" s="4">
         <v>419</v>
@@ -3248,7 +3248,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C56" s="5">
         <v>46065</v>
@@ -3260,16 +3260,16 @@
         <v>-3.1972999999999998</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J56" s="4">
         <v>999</v>
@@ -3295,7 +3295,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C57" s="5">
         <v>46065</v>
@@ -3307,16 +3307,16 @@
         <v>-3.1958600000000001</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J57" s="4">
         <v>105</v>
@@ -3342,7 +3342,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C58" s="5">
         <v>46065</v>
@@ -3354,16 +3354,16 @@
         <v>-3.19577</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4">
         <v>129</v>
@@ -3389,7 +3389,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C59" s="5">
         <v>46065</v>
@@ -3401,16 +3401,16 @@
         <v>-3.1915399999999998</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J59" s="4">
         <v>592</v>
@@ -3436,7 +3436,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C60" s="5">
         <v>46065</v>
@@ -3448,16 +3448,16 @@
         <v>-3.1937500000000001</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J60" s="4">
         <v>912</v>
@@ -3483,7 +3483,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C61" s="5">
         <v>46065</v>
@@ -3495,16 +3495,16 @@
         <v>-3.1939500000000001</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J61" s="4">
         <v>1119</v>
@@ -3530,7 +3530,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C62" s="5">
         <v>46065</v>
@@ -3542,16 +3542,16 @@
         <v>-3.1959399999999998</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J62" s="4">
         <v>511</v>
@@ -3577,7 +3577,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C63" s="5">
         <v>46065</v>
@@ -3589,16 +3589,16 @@
         <v>-3.19618</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J63" s="4">
         <v>1185</v>
@@ -3624,7 +3624,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C64" s="5">
         <v>46065</v>
@@ -3636,16 +3636,16 @@
         <v>-3.1967500000000002</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J64" s="4">
         <v>408</v>
@@ -3671,7 +3671,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C65" s="5">
         <v>46065</v>
@@ -3683,16 +3683,16 @@
         <v>-3.1997300000000002</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J65" s="4">
         <v>504</v>
@@ -3718,7 +3718,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C66" s="5">
         <v>46065</v>
@@ -3730,16 +3730,16 @@
         <v>-3.19998</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J66" s="4">
         <v>765</v>
@@ -3765,7 +3765,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C67" s="5">
         <v>46358</v>
@@ -3777,16 +3777,16 @@
         <v>-3.1936399999999998</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J67" s="4">
         <v>760</v>
@@ -3812,7 +3812,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C68" s="5">
         <v>46358</v>
@@ -3824,16 +3824,16 @@
         <v>-3.1924600000000001</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J68" s="4">
         <v>470</v>
@@ -3859,7 +3859,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C69" s="5">
         <v>46358</v>
@@ -3871,16 +3871,16 @@
         <v>-3.194</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J69" s="4">
         <v>1020</v>
@@ -3906,7 +3906,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C70" s="5">
         <v>46358</v>
@@ -3918,16 +3918,16 @@
         <v>-3.1957900000000001</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J70" s="4">
         <v>890</v>
@@ -3953,7 +3953,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C71" s="5">
         <v>46358</v>
@@ -3965,16 +3965,16 @@
         <v>-3.1964199999999998</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J71" s="4">
         <v>1130</v>
@@ -4000,7 +4000,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C72" s="5">
         <v>46358</v>
@@ -4012,16 +4012,16 @@
         <v>-3.19699</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J72" s="4">
         <v>950</v>
@@ -4047,7 +4047,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C73" s="5">
         <v>46358</v>
@@ -4059,16 +4059,16 @@
         <v>-3.19916</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J73" s="4">
         <v>690</v>
@@ -4094,10 +4094,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D74" s="4">
         <v>55.980089999999997</v>
@@ -4106,16 +4106,16 @@
         <v>-3.20052</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J74" s="4">
         <v>25</v>
@@ -4141,10 +4141,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D75" s="4">
         <v>55.951369999999997</v>
@@ -4153,16 +4153,16 @@
         <v>-3.1608000000000001</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4">
         <v>151</v>
@@ -4188,10 +4188,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D76" s="4">
         <v>55.951250000000002</v>
@@ -4200,16 +4200,16 @@
         <v>-3.1610499999999999</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4">
         <v>77</v>
@@ -4235,10 +4235,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D77" s="4">
         <v>55.950960000000002</v>
@@ -4247,16 +4247,16 @@
         <v>-3.16133</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J77" s="4">
         <v>115</v>
@@ -4282,10 +4282,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D78" s="4">
         <v>55.950839999999999</v>
@@ -4294,16 +4294,16 @@
         <v>-3.1615600000000001</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J78" s="4">
         <v>74</v>
@@ -4329,10 +4329,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D79" s="4">
         <v>55.950780000000002</v>
@@ -4341,16 +4341,16 @@
         <v>-3.1614599999999999</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J79" s="4">
         <v>84</v>
@@ -4376,10 +4376,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D80" s="4">
         <v>55.95073</v>
@@ -4388,16 +4388,16 @@
         <v>-3.1614900000000001</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4">
         <v>76</v>
@@ -4423,10 +4423,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D81" s="4">
         <v>55.950769999999999</v>
@@ -4435,16 +4435,16 @@
         <v>-3.1614200000000001</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J81" s="4">
         <v>115</v>
@@ -4470,10 +4470,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D82" s="4">
         <v>55.950719999999997</v>
@@ -4482,16 +4482,16 @@
         <v>-3.1610200000000002</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J82" s="4">
         <v>61</v>
@@ -4517,10 +4517,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D83" s="4">
         <v>55.950510000000001</v>
@@ -4529,16 +4529,16 @@
         <v>-3.1610800000000001</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J83" s="4">
         <v>346</v>
@@ -4564,10 +4564,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D84" s="4">
         <v>55.950490000000002</v>
@@ -4576,16 +4576,16 @@
         <v>-3.1610900000000002</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4">
         <v>207</v>
@@ -4611,10 +4611,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D85" s="4">
         <v>55.950479999999999</v>
@@ -4623,16 +4623,16 @@
         <v>-3.16107</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4">
         <v>67</v>
@@ -4658,10 +4658,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D86" s="9">
         <v>55.925690000000003</v>
@@ -4670,16 +4670,16 @@
         <v>-3.1920799999999998</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J86" s="4">
         <v>750</v>
@@ -4705,10 +4705,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D87" s="9">
         <v>55.925539999999998</v>
@@ -4717,16 +4717,16 @@
         <v>-3.1924000000000001</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J87" s="4">
         <v>525</v>
@@ -4752,10 +4752,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D88" s="9">
         <v>55.925409999999999</v>
@@ -4764,16 +4764,16 @@
         <v>-3.1927300000000001</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J88" s="4">
         <v>825</v>
@@ -4799,10 +4799,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D89" s="9">
         <v>55.92559</v>
@@ -4811,16 +4811,16 @@
         <v>-3.19286</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J89" s="4">
         <v>892</v>
@@ -4846,10 +4846,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D90" s="9">
         <v>55.925150000000002</v>
@@ -4858,16 +4858,16 @@
         <v>-3.1938900000000001</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J90" s="4">
         <v>515</v>
@@ -4893,10 +4893,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D91" s="9">
         <v>55.925330000000002</v>
@@ -4905,16 +4905,16 @@
         <v>-3.1939700000000002</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J91" s="4">
         <v>838</v>
@@ -4940,10 +4940,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D92" s="9">
         <v>55.925469999999997</v>
@@ -4952,16 +4952,16 @@
         <v>-3.1909900000000002</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4">
         <v>441</v>
@@ -4987,10 +4987,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D93" s="9">
         <v>55.92539</v>
@@ -4999,16 +4999,16 @@
         <v>-3.1910500000000002</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J93" s="4">
         <v>694</v>
@@ -5034,10 +5034,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D94" s="9">
         <v>55.925429999999999</v>
@@ -5046,16 +5046,16 @@
         <v>-3.1912400000000001</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4">
         <v>391</v>
@@ -5081,10 +5081,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D95" s="9">
         <v>55.925609999999999</v>
@@ -5093,16 +5093,16 @@
         <v>-3.1913999999999998</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J95" s="4">
         <v>836</v>
@@ -5128,10 +5128,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D96" s="4">
         <v>55.95682</v>
@@ -5140,16 +5140,16 @@
         <v>-3.2772999999999999</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J96" s="4">
         <v>740</v>
@@ -5175,10 +5175,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D97" s="4">
         <v>55.956879999999998</v>
@@ -5187,16 +5187,16 @@
         <v>-3.2774399999999999</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J97" s="4">
         <v>145</v>
@@ -5222,10 +5222,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D98" s="4">
         <v>55.956859999999999</v>
@@ -5234,16 +5234,16 @@
         <v>-3.27739</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J98" s="4">
         <v>865</v>
@@ -5269,10 +5269,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D99" s="4">
         <v>55.957630000000002</v>
@@ -5281,16 +5281,16 @@
         <v>-3.2770000000000001</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J99" s="4">
         <v>740</v>
@@ -5316,10 +5316,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D100" s="4">
         <v>55.957320000000003</v>
@@ -5328,16 +5328,16 @@
         <v>-3.2762600000000002</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J100" s="4">
         <v>1280</v>
@@ -5363,10 +5363,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D101" s="4">
         <v>55.957430000000002</v>
@@ -5375,16 +5375,16 @@
         <v>-3.2574299999999998</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J101" s="4">
         <v>875</v>
@@ -5410,10 +5410,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D102" s="4">
         <v>55.957369999999997</v>
@@ -5422,16 +5422,16 @@
         <v>-3.2764000000000002</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J102" s="4">
         <v>735</v>
@@ -5457,10 +5457,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D103" s="4">
         <v>55.957360000000001</v>
@@ -5469,16 +5469,16 @@
         <v>-3.2763599999999999</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J103" s="4">
         <v>767</v>
@@ -5504,10 +5504,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D104" s="4">
         <v>55.956510000000002</v>
@@ -5516,16 +5516,16 @@
         <v>-3.2758500000000002</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J104" s="4">
         <v>1333</v>
@@ -5551,10 +5551,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D105" s="4">
         <v>55.956659999999999</v>
@@ -5563,16 +5563,16 @@
         <v>-3.2759</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J105" s="4">
         <v>590</v>
@@ -5598,10 +5598,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D106" s="4">
         <v>55.953389999999999</v>
@@ -5610,16 +5610,16 @@
         <v>-3.2753700000000001</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4">
         <v>129</v>
@@ -5645,10 +5645,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D107" s="4">
         <v>55.951650000000001</v>
@@ -5657,16 +5657,16 @@
         <v>-3.2737099999999999</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J107" s="4">
         <v>615</v>
@@ -5692,10 +5692,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D108" s="4">
         <v>55.951309999999999</v>
@@ -5704,16 +5704,16 @@
         <v>-3.27366</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J108" s="4">
         <v>720</v>
@@ -5739,10 +5739,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D109" s="4">
         <v>55.951250000000002</v>
@@ -5751,16 +5751,16 @@
         <v>-3.2738</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J109" s="4">
         <v>880</v>
@@ -5786,10 +5786,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D110" s="4">
         <v>55.940809999999999</v>
@@ -5798,16 +5798,16 @@
         <v>3.1642000000000001</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J110" s="4">
         <v>21</v>
@@ -5833,10 +5833,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D111" s="4">
         <v>55.940840000000001</v>
@@ -5845,16 +5845,16 @@
         <v>3.1640199999999998</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J111" s="4">
         <v>30</v>
@@ -5880,10 +5880,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D112" s="4">
         <v>55.940660000000001</v>
@@ -5892,16 +5892,16 @@
         <v>3.1640199999999998</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J112" s="4">
         <v>30</v>
@@ -5927,10 +5927,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D113" s="4">
         <v>55.940689999999996</v>
@@ -5939,16 +5939,16 @@
         <v>3.16398</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J113" s="4">
         <v>8</v>
@@ -5974,10 +5974,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D114" s="4">
         <v>55.9405</v>
@@ -5986,16 +5986,16 @@
         <v>3.16276</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J114" s="4">
         <v>9</v>
@@ -6021,10 +6021,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D115" s="4">
         <v>55.940469999999998</v>
@@ -6033,16 +6033,16 @@
         <v>3.1625299999999998</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J115" s="4">
         <v>16</v>
@@ -6068,10 +6068,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D116" s="4">
         <v>55.940379999999998</v>
@@ -6080,16 +6080,16 @@
         <v>3.1599599999999999</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4">
         <v>6.5</v>

--- a/ferndata.xlsx
+++ b/ferndata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sallyborrowman/data_science/EEPferns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0211F44-FAE2-8640-868A-AE36AA3DFB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D1C2B2-C7F3-EC45-8FBA-E3F5A56B1BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="17240" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -197,9 +197,6 @@
     <t>Arthur's Seat</t>
   </si>
   <si>
-    <t>ftondlength</t>
-  </si>
-  <si>
     <t>numberfrond</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>bladewidth</t>
+  </si>
+  <si>
+    <t>frondlength</t>
   </si>
 </sst>
 </file>
@@ -660,7 +660,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -687,22 +687,22 @@
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="N1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
@@ -2256,7 +2256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>114</v>
       </c>

--- a/ferndata.xlsx
+++ b/ferndata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sallyborrowman/data_science/EEPferns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D1C2B2-C7F3-EC45-8FBA-E3F5A56B1BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E3C7D8-DB8A-874F-953F-B5AD88B3023E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
   </bookViews>
@@ -705,7 +705,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>55.940809999999999</v>
       </c>
       <c r="E110" s="4">
-        <v>3.1642000000000001</v>
+        <v>-3.1642000000000001</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>52</v>
@@ -5842,7 +5842,7 @@
         <v>55.940840000000001</v>
       </c>
       <c r="E111" s="4">
-        <v>3.1640199999999998</v>
+        <v>-3.1640199999999998</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>52</v>
@@ -5889,7 +5889,7 @@
         <v>55.940660000000001</v>
       </c>
       <c r="E112" s="4">
-        <v>3.1640199999999998</v>
+        <v>-3.1640199999999998</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>52</v>
@@ -5936,7 +5936,7 @@
         <v>55.940689999999996</v>
       </c>
       <c r="E113" s="4">
-        <v>3.16398</v>
+        <v>-3.16398</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>52</v>
@@ -5983,7 +5983,7 @@
         <v>55.9405</v>
       </c>
       <c r="E114" s="4">
-        <v>3.16276</v>
+        <v>-3.16276</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>52</v>
@@ -6030,7 +6030,7 @@
         <v>55.940469999999998</v>
       </c>
       <c r="E115" s="4">
-        <v>3.1625299999999998</v>
+        <v>-3.1625299999999998</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>52</v>
@@ -6077,7 +6077,7 @@
         <v>55.940379999999998</v>
       </c>
       <c r="E116" s="4">
-        <v>3.1599599999999999</v>
+        <v>-3.1599599999999999</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>52</v>

--- a/ferndata.xlsx
+++ b/ferndata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sallyborrowman/data_science/EEPferns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E3C7D8-DB8A-874F-953F-B5AD88B3023E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59290F69-B230-8643-BC42-649FC4399A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="57">
   <si>
     <t>Recorder</t>
   </si>
@@ -146,12 +146,6 @@
     <t>Grace</t>
   </si>
   <si>
-    <t>unknown - suborder Polypodiinae</t>
-  </si>
-  <si>
-    <t>unknown - genus polypodium</t>
-  </si>
-  <si>
     <t xml:space="preserve">soil </t>
   </si>
   <si>
@@ -179,9 +173,6 @@
     <t>drypoteris dilatata</t>
   </si>
   <si>
-    <t>unknown - order polypodiales</t>
-  </si>
-  <si>
     <t xml:space="preserve">dryopteris affinis </t>
   </si>
   <si>
@@ -189,9 +180,6 @@
   </si>
   <si>
     <t>Corstorphine Hill</t>
-  </si>
-  <si>
-    <t>unknown - eupolypods I</t>
   </si>
   <si>
     <t>Arthur's Seat</t>
@@ -216,6 +204,9 @@
   </si>
   <si>
     <t>frondlength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">polypodium vulgare </t>
   </si>
 </sst>
 </file>
@@ -280,7 +271,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -314,9 +305,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,7 +651,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -687,22 +678,22 @@
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="32" x14ac:dyDescent="0.2">
@@ -752,7 +743,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -799,7 +790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -893,7 +884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -940,7 +931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -987,7 +978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1034,7 +1025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1081,7 +1072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1175,7 +1166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1363,7 +1354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1598,7 +1589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2892,8 +2883,8 @@
       <c r="H48" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I48" s="8" t="s">
-        <v>36</v>
+      <c r="I48" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="J48" s="4">
         <v>20</v>
@@ -2986,8 +2977,8 @@
       <c r="H50" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I50" s="8" t="s">
-        <v>37</v>
+      <c r="I50" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="J50" s="4">
         <v>153</v>
@@ -3075,7 +3066,7 @@
         <v>30</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>24</v>
@@ -3122,7 +3113,7 @@
         <v>30</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>24</v>
@@ -3268,7 +3259,7 @@
       <c r="H56" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="4" t="s">
         <v>32</v>
       </c>
       <c r="J56" s="4">
@@ -3404,7 +3395,7 @@
         <v>30</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>24</v>
@@ -3451,13 +3442,13 @@
         <v>30</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J60" s="4">
         <v>912</v>
@@ -3686,7 +3677,7 @@
         <v>30</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>24</v>
@@ -4062,7 +4053,7 @@
         <v>30</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>24</v>
@@ -4097,7 +4088,7 @@
         <v>26</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D74" s="4">
         <v>55.980089999999997</v>
@@ -4106,7 +4097,7 @@
         <v>-3.20052</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>33</v>
@@ -4144,7 +4135,7 @@
         <v>26</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D75" s="4">
         <v>55.951369999999997</v>
@@ -4153,7 +4144,7 @@
         <v>-3.1608000000000001</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>34</v>
@@ -4191,7 +4182,7 @@
         <v>26</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D76" s="4">
         <v>55.951250000000002</v>
@@ -4200,7 +4191,7 @@
         <v>-3.1610499999999999</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>34</v>
@@ -4238,7 +4229,7 @@
         <v>26</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D77" s="4">
         <v>55.950960000000002</v>
@@ -4247,10 +4238,10 @@
         <v>-3.16133</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>11</v>
@@ -4285,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D78" s="4">
         <v>55.950839999999999</v>
@@ -4294,10 +4285,10 @@
         <v>-3.1615600000000001</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>31</v>
@@ -4332,7 +4323,7 @@
         <v>26</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D79" s="4">
         <v>55.950780000000002</v>
@@ -4341,7 +4332,7 @@
         <v>-3.1614599999999999</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>34</v>
@@ -4379,7 +4370,7 @@
         <v>26</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D80" s="4">
         <v>55.95073</v>
@@ -4388,7 +4379,7 @@
         <v>-3.1614900000000001</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>34</v>
@@ -4426,7 +4417,7 @@
         <v>26</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D81" s="4">
         <v>55.950769999999999</v>
@@ -4435,7 +4426,7 @@
         <v>-3.1614200000000001</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>34</v>
@@ -4473,7 +4464,7 @@
         <v>26</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D82" s="4">
         <v>55.950719999999997</v>
@@ -4482,7 +4473,7 @@
         <v>-3.1610200000000002</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>34</v>
@@ -4520,7 +4511,7 @@
         <v>26</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D83" s="4">
         <v>55.950510000000001</v>
@@ -4529,7 +4520,7 @@
         <v>-3.1610800000000001</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>34</v>
@@ -4538,7 +4529,7 @@
         <v>31</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J83" s="4">
         <v>346</v>
@@ -4567,7 +4558,7 @@
         <v>26</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D84" s="4">
         <v>55.950490000000002</v>
@@ -4576,7 +4567,7 @@
         <v>-3.1610900000000002</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>34</v>
@@ -4614,7 +4605,7 @@
         <v>26</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D85" s="4">
         <v>55.950479999999999</v>
@@ -4623,7 +4614,7 @@
         <v>-3.16107</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>34</v>
@@ -4661,9 +4652,9 @@
         <v>14</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D86" s="9">
+        <v>40</v>
+      </c>
+      <c r="D86" s="8">
         <v>55.925690000000003</v>
       </c>
       <c r="E86" s="4">
@@ -4673,13 +4664,13 @@
         <v>30</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J86" s="4">
         <v>750</v>
@@ -4708,9 +4699,9 @@
         <v>14</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D87" s="9">
+        <v>40</v>
+      </c>
+      <c r="D87" s="8">
         <v>55.925539999999998</v>
       </c>
       <c r="E87" s="4">
@@ -4720,13 +4711,13 @@
         <v>30</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J87" s="4">
         <v>525</v>
@@ -4755,9 +4746,9 @@
         <v>14</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D88" s="9">
+        <v>40</v>
+      </c>
+      <c r="D88" s="8">
         <v>55.925409999999999</v>
       </c>
       <c r="E88" s="4">
@@ -4767,13 +4758,13 @@
         <v>30</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J88" s="4">
         <v>825</v>
@@ -4802,9 +4793,9 @@
         <v>14</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D89" s="9">
+        <v>40</v>
+      </c>
+      <c r="D89" s="8">
         <v>55.92559</v>
       </c>
       <c r="E89" s="4">
@@ -4814,13 +4805,13 @@
         <v>30</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J89" s="4">
         <v>892</v>
@@ -4849,9 +4840,9 @@
         <v>14</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D90" s="9">
+        <v>40</v>
+      </c>
+      <c r="D90" s="8">
         <v>55.925150000000002</v>
       </c>
       <c r="E90" s="4">
@@ -4861,13 +4852,13 @@
         <v>30</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J90" s="4">
         <v>515</v>
@@ -4896,9 +4887,9 @@
         <v>14</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" s="9">
+        <v>40</v>
+      </c>
+      <c r="D91" s="8">
         <v>55.925330000000002</v>
       </c>
       <c r="E91" s="4">
@@ -4908,7 +4899,7 @@
         <v>30</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>24</v>
@@ -4943,19 +4934,19 @@
         <v>14</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D92" s="9">
+        <v>40</v>
+      </c>
+      <c r="D92" s="8">
         <v>55.925469999999997</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="8">
         <v>-3.1909900000000002</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>24</v>
@@ -4990,9 +4981,9 @@
         <v>14</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D93" s="9">
+        <v>40</v>
+      </c>
+      <c r="D93" s="8">
         <v>55.92539</v>
       </c>
       <c r="E93" s="4">
@@ -5002,13 +4993,13 @@
         <v>30</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I93" s="8" t="s">
-        <v>47</v>
+      <c r="I93" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="J93" s="4">
         <v>694</v>
@@ -5037,19 +5028,19 @@
         <v>14</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D94" s="9">
+        <v>40</v>
+      </c>
+      <c r="D94" s="8">
         <v>55.925429999999999</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="8">
         <v>-3.1912400000000001</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>24</v>
@@ -5084,25 +5075,25 @@
         <v>14</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D95" s="9">
+        <v>40</v>
+      </c>
+      <c r="D95" s="8">
         <v>55.925609999999999</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="8">
         <v>-3.1913999999999998</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J95" s="4">
         <v>836</v>
@@ -5131,7 +5122,7 @@
         <v>35</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D96" s="4">
         <v>55.95682</v>
@@ -5140,7 +5131,7 @@
         <v>-3.2772999999999999</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>24</v>
@@ -5178,7 +5169,7 @@
         <v>35</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D97" s="4">
         <v>55.956879999999998</v>
@@ -5187,7 +5178,7 @@
         <v>-3.2774399999999999</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>24</v>
@@ -5195,8 +5186,8 @@
       <c r="H97" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I97" s="8" t="s">
-        <v>47</v>
+      <c r="I97" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="J97" s="4">
         <v>145</v>
@@ -5225,7 +5216,7 @@
         <v>35</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D98" s="4">
         <v>55.956859999999999</v>
@@ -5234,7 +5225,7 @@
         <v>-3.27739</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>24</v>
@@ -5272,7 +5263,7 @@
         <v>35</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D99" s="4">
         <v>55.957630000000002</v>
@@ -5281,7 +5272,7 @@
         <v>-3.2770000000000001</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>24</v>
@@ -5319,7 +5310,7 @@
         <v>35</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D100" s="4">
         <v>55.957320000000003</v>
@@ -5328,7 +5319,7 @@
         <v>-3.2762600000000002</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>24</v>
@@ -5366,7 +5357,7 @@
         <v>35</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D101" s="4">
         <v>55.957430000000002</v>
@@ -5375,7 +5366,7 @@
         <v>-3.2574299999999998</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>24</v>
@@ -5413,7 +5404,7 @@
         <v>35</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D102" s="4">
         <v>55.957369999999997</v>
@@ -5422,7 +5413,7 @@
         <v>-3.2764000000000002</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>24</v>
@@ -5460,7 +5451,7 @@
         <v>35</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D103" s="4">
         <v>55.957360000000001</v>
@@ -5469,7 +5460,7 @@
         <v>-3.2763599999999999</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>34</v>
@@ -5477,8 +5468,8 @@
       <c r="H103" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I103" s="8" t="s">
-        <v>51</v>
+      <c r="I103" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="J103" s="4">
         <v>767</v>
@@ -5507,7 +5498,7 @@
         <v>35</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D104" s="4">
         <v>55.956510000000002</v>
@@ -5516,10 +5507,10 @@
         <v>-3.2758500000000002</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>24</v>
@@ -5554,7 +5545,7 @@
         <v>35</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D105" s="4">
         <v>55.956659999999999</v>
@@ -5563,7 +5554,7 @@
         <v>-3.2759</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>34</v>
@@ -5601,7 +5592,7 @@
         <v>35</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D106" s="4">
         <v>55.953389999999999</v>
@@ -5610,7 +5601,7 @@
         <v>-3.2753700000000001</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G106" s="4" t="s">
         <v>33</v>
@@ -5648,7 +5639,7 @@
         <v>35</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D107" s="4">
         <v>55.951650000000001</v>
@@ -5657,7 +5648,7 @@
         <v>-3.2737099999999999</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>34</v>
@@ -5695,7 +5686,7 @@
         <v>35</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D108" s="4">
         <v>55.951309999999999</v>
@@ -5704,7 +5695,7 @@
         <v>-3.27366</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>24</v>
@@ -5742,7 +5733,7 @@
         <v>35</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D109" s="4">
         <v>55.951250000000002</v>
@@ -5751,7 +5742,7 @@
         <v>-3.2738</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>24</v>
@@ -5789,7 +5780,7 @@
         <v>8</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D110" s="4">
         <v>55.940809999999999</v>
@@ -5798,7 +5789,7 @@
         <v>-3.1642000000000001</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>34</v>
@@ -5836,7 +5827,7 @@
         <v>8</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D111" s="4">
         <v>55.940840000000001</v>
@@ -5845,7 +5836,7 @@
         <v>-3.1640199999999998</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>34</v>
@@ -5883,7 +5874,7 @@
         <v>8</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D112" s="4">
         <v>55.940660000000001</v>
@@ -5892,7 +5883,7 @@
         <v>-3.1640199999999998</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>34</v>
@@ -5930,7 +5921,7 @@
         <v>8</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D113" s="4">
         <v>55.940689999999996</v>
@@ -5939,7 +5930,7 @@
         <v>-3.16398</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>34</v>
@@ -5977,7 +5968,7 @@
         <v>8</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D114" s="4">
         <v>55.9405</v>
@@ -5986,7 +5977,7 @@
         <v>-3.16276</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>10</v>
@@ -6024,7 +6015,7 @@
         <v>8</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D115" s="4">
         <v>55.940469999999998</v>
@@ -6033,7 +6024,7 @@
         <v>-3.1625299999999998</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>10</v>
@@ -6071,7 +6062,7 @@
         <v>8</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D116" s="4">
         <v>55.940379999999998</v>
@@ -6080,7 +6071,7 @@
         <v>-3.1599599999999999</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>10</v>

--- a/ferndata.xlsx
+++ b/ferndata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sallyborrowman/data_science/EEPferns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59290F69-B230-8643-BC42-649FC4399A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE97BDD-056C-A14D-88A3-4A7FC2A8B29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="56">
   <si>
     <t>Recorder</t>
   </si>
@@ -71,25 +71,10 @@
     <t>stone wall</t>
   </si>
   <si>
-    <t>concrete</t>
-  </si>
-  <si>
-    <t>asplenium adiantum-nigrum</t>
-  </si>
-  <si>
-    <t>asplenium ruta-muraria</t>
-  </si>
-  <si>
     <t>Sally</t>
   </si>
   <si>
     <t xml:space="preserve">west saville terrace </t>
-  </si>
-  <si>
-    <t>concrete wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asplenium trichomones </t>
   </si>
   <si>
     <t xml:space="preserve">blackford avenue </t>
@@ -98,19 +83,10 @@
     <t xml:space="preserve">kilgraston road </t>
   </si>
   <si>
-    <t>asplenium scolopendrium</t>
-  </si>
-  <si>
-    <t>dryopteris filix-mas</t>
-  </si>
-  <si>
     <t>grange cemetary</t>
   </si>
   <si>
     <t>newington cemetery</t>
-  </si>
-  <si>
-    <t>soil</t>
   </si>
   <si>
     <t>polystichum setiferum</t>
@@ -125,31 +101,13 @@
     <t>woodland</t>
   </si>
   <si>
-    <t>dryopteris dilatata</t>
-  </si>
-  <si>
     <t>hermitage of braid</t>
-  </si>
-  <si>
-    <t>rock</t>
-  </si>
-  <si>
-    <t>polypodium vulgare</t>
   </si>
   <si>
     <t>wall</t>
   </si>
   <si>
-    <t>natural rock</t>
-  </si>
-  <si>
     <t>Grace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil </t>
-  </si>
-  <si>
-    <t>dryopteris borreri</t>
   </si>
   <si>
     <t>2/20/2026</t>
@@ -165,15 +123,6 @@
   </si>
   <si>
     <t>ruins</t>
-  </si>
-  <si>
-    <t>dryopteris cambrensis</t>
-  </si>
-  <si>
-    <t>drypoteris dilatata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dryopteris affinis </t>
   </si>
   <si>
     <t>2/22/2026</t>
@@ -206,7 +155,55 @@
     <t>frondlength</t>
   </si>
   <si>
-    <t xml:space="preserve">polypodium vulgare </t>
+    <t xml:space="preserve">Asplenium trichomones </t>
+  </si>
+  <si>
+    <t>Asplenium ruta-muraria</t>
+  </si>
+  <si>
+    <t>Asplenium scolopendrium</t>
+  </si>
+  <si>
+    <t>Asplenium adiantum-nigrum</t>
+  </si>
+  <si>
+    <t>Dryopteris filix-mas</t>
+  </si>
+  <si>
+    <t>Dryopteris dilatata</t>
+  </si>
+  <si>
+    <t>Dryopteris borreri</t>
+  </si>
+  <si>
+    <t>Dryopteris cambrensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dryopteris affinis </t>
+  </si>
+  <si>
+    <t>Polypodium vulgare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polypodium vulgare </t>
+  </si>
+  <si>
+    <t>Wall</t>
+  </si>
+  <si>
+    <t>Wall wall</t>
+  </si>
+  <si>
+    <t>Soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil </t>
+  </si>
+  <si>
+    <t>Rock</t>
+  </si>
+  <si>
+    <t>natural Rock</t>
   </si>
 </sst>
 </file>
@@ -651,7 +648,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -678,22 +675,22 @@
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="32" x14ac:dyDescent="0.2">
@@ -719,10 +716,10 @@
         <v>10</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J2" s="4">
         <v>80</v>
@@ -766,10 +763,10 @@
         <v>10</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J3" s="4">
         <v>27</v>
@@ -795,7 +792,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5">
         <v>46236</v>
@@ -807,16 +804,16 @@
         <v>-3.18276</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J4" s="4">
         <v>58</v>
@@ -842,7 +839,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5">
         <v>46236</v>
@@ -854,16 +851,16 @@
         <v>-3.18276</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J5" s="4">
         <v>90</v>
@@ -889,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5">
         <v>46236</v>
@@ -901,16 +898,16 @@
         <v>-3.1893500000000001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J6" s="4">
         <v>36</v>
@@ -936,7 +933,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5">
         <v>46236</v>
@@ -948,16 +945,16 @@
         <v>-3.1897199999999999</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J7" s="4">
         <v>61</v>
@@ -983,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5">
         <v>46236</v>
@@ -995,16 +992,16 @@
         <v>-3.1897199999999999</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J8" s="4">
         <v>58</v>
@@ -1030,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" s="5">
         <v>46236</v>
@@ -1042,16 +1039,16 @@
         <v>-3.1928100000000001</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J9" s="4">
         <v>45</v>
@@ -1077,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5">
         <v>46236</v>
@@ -1089,16 +1086,16 @@
         <v>-3.1928100000000001</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J10" s="4">
         <v>85</v>
@@ -1124,7 +1121,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5">
         <v>46236</v>
@@ -1136,16 +1133,16 @@
         <v>-3.1931699999999998</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J11" s="4">
         <v>115</v>
@@ -1160,7 +1157,7 @@
         <v>115</v>
       </c>
       <c r="N11" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O11" s="4">
         <v>11</v>
@@ -1171,7 +1168,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5">
         <v>46236</v>
@@ -1183,16 +1180,16 @@
         <v>-3.1931699999999998</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J12" s="4">
         <v>42</v>
@@ -1218,7 +1215,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5">
         <v>46236</v>
@@ -1230,16 +1227,16 @@
         <v>-3.1933699999999998</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J13" s="4">
         <v>193</v>
@@ -1265,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5">
         <v>46236</v>
@@ -1277,16 +1274,16 @@
         <v>-3.1933699999999998</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J14" s="4">
         <v>92</v>
@@ -1312,7 +1309,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5">
         <v>46236</v>
@@ -1324,16 +1321,16 @@
         <v>-3.1938200000000001</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J15" s="4">
         <v>12</v>
@@ -1348,7 +1345,7 @@
         <v>12</v>
       </c>
       <c r="N15" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="4">
         <v>23</v>
@@ -1359,7 +1356,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5">
         <v>46236</v>
@@ -1371,16 +1368,16 @@
         <v>-3.1938200000000001</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J16" s="4">
         <v>56</v>
@@ -1406,7 +1403,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" s="5">
         <v>46236</v>
@@ -1418,16 +1415,16 @@
         <v>-3.1926999999999999</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J17" s="4">
         <v>65</v>
@@ -1453,7 +1450,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C18" s="5">
         <v>46236</v>
@@ -1465,16 +1462,16 @@
         <v>-3.1926999999999999</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J18" s="4">
         <v>107</v>
@@ -1500,7 +1497,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C19" s="5">
         <v>46236</v>
@@ -1512,16 +1509,16 @@
         <v>-3.1913900000000002</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J19" s="4">
         <v>151</v>
@@ -1536,7 +1533,7 @@
         <v>151</v>
       </c>
       <c r="N19" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O19" s="4">
         <v>14</v>
@@ -1547,7 +1544,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C20" s="5">
         <v>46236</v>
@@ -1559,16 +1556,16 @@
         <v>-3.1912699999999998</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J20" s="4">
         <v>95</v>
@@ -1594,7 +1591,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5">
         <v>46236</v>
@@ -1606,16 +1603,16 @@
         <v>-3.1912699999999998</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J21" s="4">
         <v>19</v>
@@ -1641,7 +1638,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C22" s="5">
         <v>46236</v>
@@ -1653,16 +1650,16 @@
         <v>-3.1911800000000001</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J22" s="4">
         <v>121</v>
@@ -1688,7 +1685,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C23" s="5">
         <v>46236</v>
@@ -1700,16 +1697,16 @@
         <v>-3.1908300000000001</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J23" s="4">
         <v>89</v>
@@ -1724,7 +1721,7 @@
         <v>89</v>
       </c>
       <c r="N23" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O23" s="4">
         <v>12</v>
@@ -1747,16 +1744,16 @@
         <v>-3.1641900000000001</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J24" s="4">
         <v>540</v>
@@ -1794,16 +1791,16 @@
         <v>-3.1642800000000002</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J25" s="4">
         <v>610</v>
@@ -1841,16 +1838,16 @@
         <v>-3.1651199999999999</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J26" s="4">
         <v>205</v>
@@ -1888,16 +1885,16 @@
         <v>-3.1652800000000001</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J27" s="4">
         <v>200</v>
@@ -1935,16 +1932,16 @@
         <v>-3.16736</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J28" s="4">
         <v>580</v>
@@ -1982,16 +1979,16 @@
         <v>-3.1672600000000002</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4">
         <v>800</v>
@@ -2017,7 +2014,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C30" s="5">
         <v>46065</v>
@@ -2029,16 +2026,16 @@
         <v>-3.1930000000000001</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J30" s="4">
         <v>110</v>
@@ -2064,7 +2061,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C31" s="5">
         <v>46065</v>
@@ -2076,16 +2073,16 @@
         <v>-3.1931799999999999</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J31" s="4">
         <v>126</v>
@@ -2111,7 +2108,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C32" s="5">
         <v>46065</v>
@@ -2123,16 +2120,16 @@
         <v>-3.1942699999999999</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J32" s="4">
         <v>498</v>
@@ -2158,7 +2155,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C33" s="5">
         <v>46065</v>
@@ -2170,16 +2167,16 @@
         <v>-3.1945000000000001</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J33" s="4">
         <v>265</v>
@@ -2205,7 +2202,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C34" s="5">
         <v>46065</v>
@@ -2217,16 +2214,16 @@
         <v>-3.1955900000000002</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J34" s="4">
         <v>110</v>
@@ -2252,7 +2249,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C35" s="5">
         <v>46065</v>
@@ -2264,16 +2261,16 @@
         <v>-3.1966800000000002</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J35" s="4">
         <v>121</v>
@@ -2299,7 +2296,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C36" s="5">
         <v>46065</v>
@@ -2311,16 +2308,16 @@
         <v>-3.1967699999999999</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J36" s="4">
         <v>148</v>
@@ -2346,7 +2343,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C37" s="5">
         <v>46065</v>
@@ -2358,16 +2355,16 @@
         <v>-3.1968200000000002</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J37" s="4">
         <v>177</v>
@@ -2393,7 +2390,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C38" s="5">
         <v>46065</v>
@@ -2405,16 +2402,16 @@
         <v>-3.19679</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J38" s="4">
         <v>135</v>
@@ -2440,7 +2437,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C39" s="5">
         <v>46065</v>
@@ -2452,16 +2449,16 @@
         <v>-3.1968999999999999</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J39" s="4">
         <v>174</v>
@@ -2487,7 +2484,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C40" s="5">
         <v>46065</v>
@@ -2499,16 +2496,16 @@
         <v>-3.19678</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J40" s="4">
         <v>267</v>
@@ -2534,7 +2531,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C41" s="5">
         <v>46065</v>
@@ -2546,16 +2543,16 @@
         <v>-3.1966299999999999</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J41" s="4">
         <v>109</v>
@@ -2581,7 +2578,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C42" s="5">
         <v>46065</v>
@@ -2593,16 +2590,16 @@
         <v>-3.1911100000000001</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J42" s="4">
         <v>870</v>
@@ -2640,16 +2637,16 @@
         <v>-3.1938399999999998</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J43" s="4">
         <v>42</v>
@@ -2687,16 +2684,16 @@
         <v>-3.1968299999999998</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J44" s="4">
         <v>34</v>
@@ -2734,16 +2731,16 @@
         <v>-3.1967400000000001</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J45" s="4">
         <v>22</v>
@@ -2781,16 +2778,16 @@
         <v>-3.1972800000000001</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J46" s="4">
         <v>28</v>
@@ -2828,16 +2825,16 @@
         <v>-3.1960799999999998</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J47" s="4">
         <v>6</v>
@@ -2852,7 +2849,7 @@
         <v>6</v>
       </c>
       <c r="N47" s="4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -2863,7 +2860,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C48" s="5">
         <v>46358</v>
@@ -2875,16 +2872,16 @@
         <v>-3.1968100000000002</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J48" s="4">
         <v>20</v>
@@ -2910,7 +2907,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C49" s="5">
         <v>46065</v>
@@ -2922,16 +2919,16 @@
         <v>-3.19659</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J49" s="4">
         <v>296</v>
@@ -2957,7 +2954,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C50" s="5">
         <v>46065</v>
@@ -2969,16 +2966,16 @@
         <v>-3.1957100000000001</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J50" s="4">
         <v>153</v>
@@ -3004,7 +3001,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C51" s="5">
         <v>46358</v>
@@ -3016,16 +3013,16 @@
         <v>-3.1915200000000001</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J51" s="4">
         <v>550</v>
@@ -3051,7 +3048,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C52" s="5">
         <v>46065</v>
@@ -3063,16 +3060,16 @@
         <v>-3.1932</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J52" s="4">
         <v>190</v>
@@ -3098,7 +3095,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C53" s="5">
         <v>46065</v>
@@ -3110,16 +3107,16 @@
         <v>-3.1938200000000001</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J53" s="4">
         <v>495</v>
@@ -3145,7 +3142,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C54" s="5">
         <v>46065</v>
@@ -3157,16 +3154,16 @@
         <v>-3.1969099999999999</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J54" s="4">
         <v>94</v>
@@ -3192,7 +3189,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C55" s="5">
         <v>46065</v>
@@ -3204,16 +3201,16 @@
         <v>-3.1970700000000001</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J55" s="4">
         <v>419</v>
@@ -3239,7 +3236,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C56" s="5">
         <v>46065</v>
@@ -3251,16 +3248,16 @@
         <v>-3.1972999999999998</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J56" s="4">
         <v>999</v>
@@ -3286,7 +3283,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C57" s="5">
         <v>46065</v>
@@ -3298,16 +3295,16 @@
         <v>-3.1958600000000001</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J57" s="4">
         <v>105</v>
@@ -3333,7 +3330,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C58" s="5">
         <v>46065</v>
@@ -3345,16 +3342,16 @@
         <v>-3.19577</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J58" s="4">
         <v>129</v>
@@ -3380,7 +3377,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C59" s="5">
         <v>46065</v>
@@ -3392,16 +3389,16 @@
         <v>-3.1915399999999998</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J59" s="4">
         <v>592</v>
@@ -3427,7 +3424,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C60" s="5">
         <v>46065</v>
@@ -3439,16 +3436,16 @@
         <v>-3.1937500000000001</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J60" s="4">
         <v>912</v>
@@ -3474,7 +3471,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C61" s="5">
         <v>46065</v>
@@ -3486,16 +3483,16 @@
         <v>-3.1939500000000001</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J61" s="4">
         <v>1119</v>
@@ -3521,7 +3518,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C62" s="5">
         <v>46065</v>
@@ -3533,16 +3530,16 @@
         <v>-3.1959399999999998</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J62" s="4">
         <v>511</v>
@@ -3568,7 +3565,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C63" s="5">
         <v>46065</v>
@@ -3580,16 +3577,16 @@
         <v>-3.19618</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J63" s="4">
         <v>1185</v>
@@ -3615,7 +3612,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C64" s="5">
         <v>46065</v>
@@ -3627,16 +3624,16 @@
         <v>-3.1967500000000002</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J64" s="4">
         <v>408</v>
@@ -3662,7 +3659,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C65" s="5">
         <v>46065</v>
@@ -3674,16 +3671,16 @@
         <v>-3.1997300000000002</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J65" s="4">
         <v>504</v>
@@ -3709,7 +3706,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C66" s="5">
         <v>46065</v>
@@ -3721,16 +3718,16 @@
         <v>-3.19998</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J66" s="4">
         <v>765</v>
@@ -3756,7 +3753,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C67" s="5">
         <v>46358</v>
@@ -3768,16 +3765,16 @@
         <v>-3.1936399999999998</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J67" s="4">
         <v>760</v>
@@ -3803,7 +3800,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C68" s="5">
         <v>46358</v>
@@ -3815,16 +3812,16 @@
         <v>-3.1924600000000001</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J68" s="4">
         <v>470</v>
@@ -3850,7 +3847,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C69" s="5">
         <v>46358</v>
@@ -3862,16 +3859,16 @@
         <v>-3.194</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J69" s="4">
         <v>1020</v>
@@ -3897,7 +3894,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C70" s="5">
         <v>46358</v>
@@ -3909,16 +3906,16 @@
         <v>-3.1957900000000001</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J70" s="4">
         <v>890</v>
@@ -3944,7 +3941,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C71" s="5">
         <v>46358</v>
@@ -3956,16 +3953,16 @@
         <v>-3.1964199999999998</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J71" s="4">
         <v>1130</v>
@@ -3991,7 +3988,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C72" s="5">
         <v>46358</v>
@@ -4003,16 +4000,16 @@
         <v>-3.19699</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J72" s="4">
         <v>950</v>
@@ -4038,7 +4035,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C73" s="5">
         <v>46358</v>
@@ -4050,16 +4047,16 @@
         <v>-3.19916</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J73" s="4">
         <v>690</v>
@@ -4085,10 +4082,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D74" s="4">
         <v>55.980089999999997</v>
@@ -4097,16 +4094,16 @@
         <v>-3.20052</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J74" s="4">
         <v>25</v>
@@ -4132,10 +4129,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D75" s="4">
         <v>55.951369999999997</v>
@@ -4144,16 +4141,16 @@
         <v>-3.1608000000000001</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J75" s="4">
         <v>151</v>
@@ -4179,10 +4176,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D76" s="4">
         <v>55.951250000000002</v>
@@ -4191,16 +4188,16 @@
         <v>-3.1610499999999999</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J76" s="4">
         <v>77</v>
@@ -4226,10 +4223,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D77" s="4">
         <v>55.950960000000002</v>
@@ -4238,16 +4235,16 @@
         <v>-3.16133</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G77" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I77" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="J77" s="4">
         <v>115</v>
@@ -4273,10 +4270,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D78" s="4">
         <v>55.950839999999999</v>
@@ -4285,16 +4282,16 @@
         <v>-3.1615600000000001</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G78" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="J78" s="4">
         <v>74</v>
@@ -4320,10 +4317,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D79" s="4">
         <v>55.950780000000002</v>
@@ -4332,16 +4329,16 @@
         <v>-3.1614599999999999</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J79" s="4">
         <v>84</v>
@@ -4367,10 +4364,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D80" s="4">
         <v>55.95073</v>
@@ -4379,16 +4376,16 @@
         <v>-3.1614900000000001</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J80" s="4">
         <v>76</v>
@@ -4414,10 +4411,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D81" s="4">
         <v>55.950769999999999</v>
@@ -4426,16 +4423,16 @@
         <v>-3.1614200000000001</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J81" s="4">
         <v>115</v>
@@ -4461,10 +4458,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D82" s="4">
         <v>55.950719999999997</v>
@@ -4473,16 +4470,16 @@
         <v>-3.1610200000000002</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J82" s="4">
         <v>61</v>
@@ -4508,10 +4505,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D83" s="4">
         <v>55.950510000000001</v>
@@ -4520,16 +4517,16 @@
         <v>-3.1610800000000001</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J83" s="4">
         <v>346</v>
@@ -4555,10 +4552,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D84" s="4">
         <v>55.950490000000002</v>
@@ -4567,16 +4564,16 @@
         <v>-3.1610900000000002</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J84" s="4">
         <v>207</v>
@@ -4602,10 +4599,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D85" s="4">
         <v>55.950479999999999</v>
@@ -4614,16 +4611,16 @@
         <v>-3.16107</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J85" s="4">
         <v>67</v>
@@ -4649,10 +4646,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D86" s="8">
         <v>55.925690000000003</v>
@@ -4661,13 +4658,13 @@
         <v>-3.1920799999999998</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>44</v>
@@ -4696,10 +4693,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D87" s="8">
         <v>55.925539999999998</v>
@@ -4708,13 +4705,13 @@
         <v>-3.1924000000000001</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>44</v>
@@ -4743,10 +4740,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D88" s="8">
         <v>55.925409999999999</v>
@@ -4755,13 +4752,13 @@
         <v>-3.1927300000000001</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>44</v>
@@ -4790,10 +4787,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D89" s="8">
         <v>55.92559</v>
@@ -4802,13 +4799,13 @@
         <v>-3.19286</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>44</v>
@@ -4837,10 +4834,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D90" s="8">
         <v>55.925150000000002</v>
@@ -4849,13 +4846,13 @@
         <v>-3.1938900000000001</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>44</v>
@@ -4884,10 +4881,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D91" s="8">
         <v>55.925330000000002</v>
@@ -4896,16 +4893,16 @@
         <v>-3.1939700000000002</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J91" s="4">
         <v>838</v>
@@ -4931,10 +4928,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D92" s="8">
         <v>55.925469999999997</v>
@@ -4943,16 +4940,16 @@
         <v>-3.1909900000000002</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J92" s="4">
         <v>441</v>
@@ -4978,10 +4975,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D93" s="8">
         <v>55.92539</v>
@@ -4990,16 +4987,16 @@
         <v>-3.1910500000000002</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J93" s="4">
         <v>694</v>
@@ -5025,10 +5022,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D94" s="8">
         <v>55.925429999999999</v>
@@ -5037,16 +5034,16 @@
         <v>-3.1912400000000001</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J94" s="4">
         <v>391</v>
@@ -5072,10 +5069,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D95" s="8">
         <v>55.925609999999999</v>
@@ -5084,16 +5081,16 @@
         <v>-3.1913999999999998</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J95" s="4">
         <v>836</v>
@@ -5119,10 +5116,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D96" s="4">
         <v>55.95682</v>
@@ -5131,16 +5128,16 @@
         <v>-3.2772999999999999</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J96" s="4">
         <v>740</v>
@@ -5166,10 +5163,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D97" s="4">
         <v>55.956879999999998</v>
@@ -5178,16 +5175,16 @@
         <v>-3.2774399999999999</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J97" s="4">
         <v>145</v>
@@ -5213,10 +5210,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D98" s="4">
         <v>55.956859999999999</v>
@@ -5225,16 +5222,16 @@
         <v>-3.27739</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J98" s="4">
         <v>865</v>
@@ -5260,10 +5257,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D99" s="4">
         <v>55.957630000000002</v>
@@ -5272,16 +5269,16 @@
         <v>-3.2770000000000001</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J99" s="4">
         <v>740</v>
@@ -5307,10 +5304,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D100" s="4">
         <v>55.957320000000003</v>
@@ -5319,16 +5316,16 @@
         <v>-3.2762600000000002</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J100" s="4">
         <v>1280</v>
@@ -5354,10 +5351,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D101" s="4">
         <v>55.957430000000002</v>
@@ -5366,16 +5363,16 @@
         <v>-3.2574299999999998</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J101" s="4">
         <v>875</v>
@@ -5401,10 +5398,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D102" s="4">
         <v>55.957369999999997</v>
@@ -5413,16 +5410,16 @@
         <v>-3.2764000000000002</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J102" s="4">
         <v>735</v>
@@ -5448,10 +5445,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D103" s="4">
         <v>55.957360000000001</v>
@@ -5460,16 +5457,16 @@
         <v>-3.2763599999999999</v>
       </c>
       <c r="F103" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I103" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H103" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I103" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="J103" s="4">
         <v>767</v>
@@ -5495,10 +5492,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D104" s="4">
         <v>55.956510000000002</v>
@@ -5507,16 +5504,16 @@
         <v>-3.2758500000000002</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J104" s="4">
         <v>1333</v>
@@ -5542,10 +5539,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D105" s="4">
         <v>55.956659999999999</v>
@@ -5554,16 +5551,16 @@
         <v>-3.2759</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J105" s="4">
         <v>590</v>
@@ -5589,10 +5586,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D106" s="4">
         <v>55.953389999999999</v>
@@ -5601,16 +5598,16 @@
         <v>-3.2753700000000001</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J106" s="4">
         <v>129</v>
@@ -5636,10 +5633,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D107" s="4">
         <v>55.951650000000001</v>
@@ -5648,16 +5645,16 @@
         <v>-3.2737099999999999</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J107" s="4">
         <v>615</v>
@@ -5683,10 +5680,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D108" s="4">
         <v>55.951309999999999</v>
@@ -5695,16 +5692,16 @@
         <v>-3.27366</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J108" s="4">
         <v>720</v>
@@ -5730,10 +5727,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D109" s="4">
         <v>55.951250000000002</v>
@@ -5742,16 +5739,16 @@
         <v>-3.2738</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J109" s="4">
         <v>880</v>
@@ -5780,7 +5777,7 @@
         <v>8</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D110" s="4">
         <v>55.940809999999999</v>
@@ -5789,16 +5786,16 @@
         <v>-3.1642000000000001</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J110" s="4">
         <v>21</v>
@@ -5827,7 +5824,7 @@
         <v>8</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D111" s="4">
         <v>55.940840000000001</v>
@@ -5836,16 +5833,16 @@
         <v>-3.1640199999999998</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J111" s="4">
         <v>30</v>
@@ -5874,7 +5871,7 @@
         <v>8</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D112" s="4">
         <v>55.940660000000001</v>
@@ -5883,16 +5880,16 @@
         <v>-3.1640199999999998</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J112" s="4">
         <v>30</v>
@@ -5921,7 +5918,7 @@
         <v>8</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D113" s="4">
         <v>55.940689999999996</v>
@@ -5930,16 +5927,16 @@
         <v>-3.16398</v>
       </c>
       <c r="F113" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I113" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I113" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="J113" s="4">
         <v>8</v>
@@ -5968,7 +5965,7 @@
         <v>8</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D114" s="4">
         <v>55.9405</v>
@@ -5977,16 +5974,16 @@
         <v>-3.16276</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J114" s="4">
         <v>9</v>
@@ -6015,7 +6012,7 @@
         <v>8</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D115" s="4">
         <v>55.940469999999998</v>
@@ -6024,16 +6021,16 @@
         <v>-3.1625299999999998</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J115" s="4">
         <v>16</v>
@@ -6062,7 +6059,7 @@
         <v>8</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D116" s="4">
         <v>55.940379999999998</v>
@@ -6071,16 +6068,16 @@
         <v>-3.1599599999999999</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J116" s="4">
         <v>6.5</v>

--- a/ferndata.xlsx
+++ b/ferndata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sallyborrowman/data_science/EEPferns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE97BDD-056C-A14D-88A3-4A7FC2A8B29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDA93BF-B426-314B-95ED-A101EFCB7CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9AD53EB6-C9C2-FE4D-9C48-157E59570A93}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="54">
   <si>
     <t>Recorder</t>
   </si>
@@ -171,12 +171,6 @@
   </si>
   <si>
     <t>Dryopteris dilatata</t>
-  </si>
-  <si>
-    <t>Dryopteris borreri</t>
-  </si>
-  <si>
-    <t>Dryopteris cambrensis</t>
   </si>
   <si>
     <t xml:space="preserve">Dryopteris affinis </t>
@@ -639,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3765A508-6B07-7645-B149-33C1FB7C5981}">
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="13" customWidth="1"/>
@@ -716,7 +710,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>42</v>
@@ -763,7 +757,7 @@
         <v>10</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>40</v>
@@ -807,10 +801,10 @@
         <v>12</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>40</v>
@@ -854,10 +848,10 @@
         <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>39</v>
@@ -904,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>40</v>
@@ -951,7 +945,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>40</v>
@@ -998,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>40</v>
@@ -1045,7 +1039,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>42</v>
@@ -1092,7 +1086,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>40</v>
@@ -1139,7 +1133,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>39</v>
@@ -1186,7 +1180,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>40</v>
@@ -1233,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>41</v>
@@ -1280,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>43</v>
@@ -1327,7 +1321,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>39</v>
@@ -1374,7 +1368,7 @@
         <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>40</v>
@@ -1421,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>39</v>
@@ -1468,7 +1462,7 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>39</v>
@@ -1515,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>39</v>
@@ -1562,7 +1556,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>39</v>
@@ -1609,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>40</v>
@@ -1656,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>39</v>
@@ -1703,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>39</v>
@@ -1747,10 +1741,10 @@
         <v>16</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>41</v>
@@ -1794,10 +1788,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>17</v>
@@ -1844,7 +1838,7 @@
         <v>10</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>41</v>
@@ -1891,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>43</v>
@@ -1935,10 +1929,10 @@
         <v>16</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>41</v>
@@ -1982,10 +1976,10 @@
         <v>16</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>17</v>
@@ -2029,10 +2023,10 @@
         <v>19</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>42</v>
@@ -2076,10 +2070,10 @@
         <v>19</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>42</v>
@@ -2126,7 +2120,7 @@
         <v>20</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>44</v>
@@ -2173,7 +2167,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>41</v>
@@ -2220,7 +2214,7 @@
         <v>20</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>42</v>
@@ -2267,10 +2261,10 @@
         <v>20</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J35" s="4">
         <v>121</v>
@@ -2314,10 +2308,10 @@
         <v>20</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J36" s="4">
         <v>148</v>
@@ -2361,10 +2355,10 @@
         <v>20</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J37" s="4">
         <v>177</v>
@@ -2408,10 +2402,10 @@
         <v>20</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J38" s="4">
         <v>135</v>
@@ -2455,10 +2449,10 @@
         <v>20</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J39" s="4">
         <v>174</v>
@@ -2502,10 +2496,10 @@
         <v>20</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J40" s="4">
         <v>267</v>
@@ -2549,7 +2543,7 @@
         <v>22</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>39</v>
@@ -2596,7 +2590,7 @@
         <v>20</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>43</v>
@@ -2640,10 +2634,10 @@
         <v>21</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>41</v>
@@ -2687,13 +2681,13 @@
         <v>21</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J44" s="4">
         <v>34</v>
@@ -2734,13 +2728,13 @@
         <v>21</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J45" s="4">
         <v>22</v>
@@ -2781,13 +2775,13 @@
         <v>21</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J46" s="4">
         <v>28</v>
@@ -2831,7 +2825,7 @@
         <v>22</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>39</v>
@@ -2875,13 +2869,13 @@
         <v>21</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J48" s="4">
         <v>20</v>
@@ -2925,7 +2919,7 @@
         <v>22</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>41</v>
@@ -2972,10 +2966,10 @@
         <v>22</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J50" s="4">
         <v>153</v>
@@ -3016,10 +3010,10 @@
         <v>21</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>44</v>
@@ -3063,10 +3057,10 @@
         <v>21</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>44</v>
@@ -3110,10 +3104,10 @@
         <v>21</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>43</v>
@@ -3157,13 +3151,13 @@
         <v>21</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J54" s="4">
         <v>94</v>
@@ -3204,10 +3198,10 @@
         <v>21</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>43</v>
@@ -3251,13 +3245,13 @@
         <v>21</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J56" s="4">
         <v>999</v>
@@ -3301,7 +3295,7 @@
         <v>22</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>41</v>
@@ -3348,7 +3342,7 @@
         <v>22</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>41</v>
@@ -3392,10 +3386,10 @@
         <v>21</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>44</v>
@@ -3421,7 +3415,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>11</v>
@@ -3430,10 +3424,10 @@
         <v>46065</v>
       </c>
       <c r="D60" s="4">
-        <v>55.921300000000002</v>
+        <v>55.92042</v>
       </c>
       <c r="E60" s="4">
-        <v>-3.1937500000000001</v>
+        <v>-3.1939500000000001</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>21</v>
@@ -3445,30 +3439,30 @@
         <v>52</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J60" s="4">
-        <v>912</v>
+        <v>1119</v>
       </c>
       <c r="K60" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L60" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M60" s="4">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="N60" s="4">
-        <v>173</v>
+        <v>374</v>
       </c>
       <c r="O60" s="4">
-        <v>319</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>11</v>
@@ -3477,45 +3471,45 @@
         <v>46065</v>
       </c>
       <c r="D61" s="4">
-        <v>55.92042</v>
+        <v>55.920299999999997</v>
       </c>
       <c r="E61" s="4">
-        <v>-3.1939500000000001</v>
+        <v>-3.1959399999999998</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J61" s="4">
-        <v>1119</v>
+        <v>511</v>
       </c>
       <c r="K61" s="4">
         <v>5</v>
       </c>
       <c r="L61" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M61" s="4">
-        <v>745</v>
+        <v>294</v>
       </c>
       <c r="N61" s="4">
-        <v>374</v>
+        <v>217</v>
       </c>
       <c r="O61" s="4">
-        <v>236</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>11</v>
@@ -3524,45 +3518,45 @@
         <v>46065</v>
       </c>
       <c r="D62" s="4">
-        <v>55.920299999999997</v>
+        <v>55.920360000000002</v>
       </c>
       <c r="E62" s="4">
-        <v>-3.1959399999999998</v>
+        <v>-3.19618</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J62" s="4">
-        <v>511</v>
+        <v>1185</v>
       </c>
       <c r="K62" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M62" s="4">
-        <v>294</v>
+        <v>745</v>
       </c>
       <c r="N62" s="4">
-        <v>217</v>
+        <v>440</v>
       </c>
       <c r="O62" s="4">
-        <v>102</v>
+        <v>369</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>11</v>
@@ -3571,45 +3565,45 @@
         <v>46065</v>
       </c>
       <c r="D63" s="4">
-        <v>55.920360000000002</v>
+        <v>55.920349999999999</v>
       </c>
       <c r="E63" s="4">
-        <v>-3.19618</v>
+        <v>-3.1967500000000002</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J63" s="4">
-        <v>1185</v>
+        <v>408</v>
       </c>
       <c r="K63" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L63" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M63" s="4">
-        <v>745</v>
+        <v>303</v>
       </c>
       <c r="N63" s="4">
-        <v>440</v>
+        <v>105</v>
       </c>
       <c r="O63" s="4">
-        <v>369</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>11</v>
@@ -3618,45 +3612,45 @@
         <v>46065</v>
       </c>
       <c r="D64" s="4">
-        <v>55.920349999999999</v>
+        <v>55.920090000000002</v>
       </c>
       <c r="E64" s="4">
-        <v>-3.1967500000000002</v>
+        <v>-3.1997300000000002</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J64" s="4">
-        <v>408</v>
+        <v>504</v>
       </c>
       <c r="K64" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L64" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="4">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="N64" s="4">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="O64" s="4">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>11</v>
@@ -3665,10 +3659,10 @@
         <v>46065</v>
       </c>
       <c r="D65" s="4">
-        <v>55.920090000000002</v>
+        <v>55.919899999999998</v>
       </c>
       <c r="E65" s="4">
-        <v>-3.1997300000000002</v>
+        <v>-3.19998</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>21</v>
@@ -3680,77 +3674,77 @@
         <v>52</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J65" s="4">
-        <v>504</v>
+        <v>765</v>
       </c>
       <c r="K65" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L65" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M65" s="4">
-        <v>381</v>
+        <v>600</v>
       </c>
       <c r="N65" s="4">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="O65" s="4">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C66" s="5">
-        <v>46065</v>
+        <v>46358</v>
       </c>
       <c r="D66" s="4">
-        <v>55.919899999999998</v>
+        <v>55.911819999999999</v>
       </c>
       <c r="E66" s="4">
-        <v>-3.19998</v>
+        <v>-3.1936399999999998</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J66" s="4">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="K66" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L66" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M66" s="4">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="N66" s="4">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="O66" s="4">
-        <v>176</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>23</v>
@@ -3759,45 +3753,45 @@
         <v>46358</v>
       </c>
       <c r="D67" s="4">
-        <v>55.911819999999999</v>
+        <v>55.919919999999998</v>
       </c>
       <c r="E67" s="4">
-        <v>-3.1936399999999998</v>
+        <v>-3.1924600000000001</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J67" s="4">
-        <v>760</v>
+        <v>470</v>
       </c>
       <c r="K67" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L67" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M67" s="4">
-        <v>690</v>
+        <v>320</v>
       </c>
       <c r="N67" s="4">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="O67" s="4">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>23</v>
@@ -3806,45 +3800,45 @@
         <v>46358</v>
       </c>
       <c r="D68" s="4">
-        <v>55.919919999999998</v>
+        <v>55.920430000000003</v>
       </c>
       <c r="E68" s="4">
-        <v>-3.1924600000000001</v>
+        <v>-3.194</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J68" s="4">
-        <v>470</v>
+        <v>1020</v>
       </c>
       <c r="K68" s="4">
         <v>6</v>
       </c>
       <c r="L68" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M68" s="4">
-        <v>320</v>
+        <v>650</v>
       </c>
       <c r="N68" s="4">
-        <v>150</v>
+        <v>370</v>
       </c>
       <c r="O68" s="4">
-        <v>200</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>23</v>
@@ -3853,28 +3847,28 @@
         <v>46358</v>
       </c>
       <c r="D69" s="4">
-        <v>55.920430000000003</v>
+        <v>55.920140000000004</v>
       </c>
       <c r="E69" s="4">
-        <v>-3.194</v>
+        <v>-3.1957900000000001</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J69" s="4">
-        <v>1020</v>
+        <v>890</v>
       </c>
       <c r="K69" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L69" s="4">
         <v>6</v>
@@ -3883,15 +3877,15 @@
         <v>650</v>
       </c>
       <c r="N69" s="4">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="O69" s="4">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>23</v>
@@ -3900,45 +3894,45 @@
         <v>46358</v>
       </c>
       <c r="D70" s="4">
-        <v>55.920140000000004</v>
+        <v>55.920349999999999</v>
       </c>
       <c r="E70" s="4">
-        <v>-3.1957900000000001</v>
+        <v>-3.1964199999999998</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J70" s="4">
-        <v>890</v>
+        <v>1130</v>
       </c>
       <c r="K70" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L70" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M70" s="4">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="N70" s="4">
-        <v>240</v>
+        <v>530</v>
       </c>
       <c r="O70" s="4">
-        <v>230</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>23</v>
@@ -3947,45 +3941,45 @@
         <v>46358</v>
       </c>
       <c r="D71" s="4">
-        <v>55.920349999999999</v>
+        <v>55.920293000000001</v>
       </c>
       <c r="E71" s="4">
-        <v>-3.1964199999999998</v>
+        <v>-3.19699</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J71" s="4">
-        <v>1130</v>
+        <v>950</v>
       </c>
       <c r="K71" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L71" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M71" s="4">
-        <v>600</v>
+        <v>730</v>
       </c>
       <c r="N71" s="4">
-        <v>530</v>
+        <v>220</v>
       </c>
       <c r="O71" s="4">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>23</v>
@@ -3994,139 +3988,139 @@
         <v>46358</v>
       </c>
       <c r="D72" s="4">
-        <v>55.920293000000001</v>
+        <v>55.920140000000004</v>
       </c>
       <c r="E72" s="4">
-        <v>-3.19699</v>
+        <v>-3.19916</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J72" s="4">
-        <v>950</v>
+        <v>690</v>
       </c>
       <c r="K72" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L72" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M72" s="4">
-        <v>730</v>
+        <v>420</v>
       </c>
       <c r="N72" s="4">
+        <v>270</v>
+      </c>
+      <c r="O72" s="4">
         <v>220</v>
-      </c>
-      <c r="O72" s="4">
-        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46358</v>
+        <v>18</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="D73" s="4">
-        <v>55.920140000000004</v>
+        <v>55.980089999999997</v>
       </c>
       <c r="E73" s="4">
-        <v>-3.19916</v>
+        <v>-3.20052</v>
       </c>
       <c r="F73" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J73" s="4">
+        <v>25</v>
+      </c>
+      <c r="K73" s="4">
+        <v>6</v>
+      </c>
+      <c r="L73" s="4">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4">
         <v>21</v>
       </c>
-      <c r="G73" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J73" s="4">
-        <v>690</v>
-      </c>
-      <c r="K73" s="4">
-        <v>8</v>
-      </c>
-      <c r="L73" s="4">
-        <v>8</v>
-      </c>
-      <c r="M73" s="4">
-        <v>420</v>
-      </c>
       <c r="N73" s="4">
-        <v>270</v>
+        <v>4</v>
       </c>
       <c r="O73" s="4">
-        <v>220</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D74" s="4">
-        <v>55.980089999999997</v>
+        <v>55.951369999999997</v>
       </c>
       <c r="E74" s="4">
-        <v>-3.20052</v>
+        <v>-3.1608000000000001</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J74" s="4">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="K74" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L74" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="N74" s="4">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="O74" s="4">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>18</v>
@@ -4135,45 +4129,45 @@
         <v>26</v>
       </c>
       <c r="D75" s="4">
-        <v>55.951369999999997</v>
+        <v>55.951250000000002</v>
       </c>
       <c r="E75" s="4">
-        <v>-3.1608000000000001</v>
+        <v>-3.1610499999999999</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J75" s="4">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="K75" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L75" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="4">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="N75" s="4">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="O75" s="4">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>18</v>
@@ -4182,45 +4176,45 @@
         <v>26</v>
       </c>
       <c r="D76" s="4">
-        <v>55.951250000000002</v>
+        <v>55.950960000000002</v>
       </c>
       <c r="E76" s="4">
-        <v>-3.1610499999999999</v>
+        <v>-3.16133</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J76" s="4">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="K76" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L76" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M76" s="4">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="N76" s="4">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="O76" s="4">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>18</v>
@@ -4229,10 +4223,10 @@
         <v>26</v>
       </c>
       <c r="D77" s="4">
-        <v>55.950960000000002</v>
+        <v>55.950839999999999</v>
       </c>
       <c r="E77" s="4">
-        <v>-3.16133</v>
+        <v>-3.1615600000000001</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>27</v>
@@ -4241,33 +4235,33 @@
         <v>28</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J77" s="4">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="K77" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L77" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77" s="4">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="N77" s="4">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="O77" s="4">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>18</v>
@@ -4276,45 +4270,45 @@
         <v>26</v>
       </c>
       <c r="D78" s="4">
-        <v>55.950839999999999</v>
+        <v>55.950780000000002</v>
       </c>
       <c r="E78" s="4">
-        <v>-3.1615600000000001</v>
+        <v>-3.1614599999999999</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J78" s="4">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K78" s="4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L78" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M78" s="4">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="N78" s="4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O78" s="4">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>18</v>
@@ -4323,45 +4317,45 @@
         <v>26</v>
       </c>
       <c r="D79" s="4">
-        <v>55.950780000000002</v>
+        <v>55.95073</v>
       </c>
       <c r="E79" s="4">
-        <v>-3.1614599999999999</v>
+        <v>-3.1614900000000001</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J79" s="4">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="K79" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L79" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M79" s="4">
         <v>57</v>
       </c>
       <c r="N79" s="4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="O79" s="4">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>18</v>
@@ -4370,45 +4364,45 @@
         <v>26</v>
       </c>
       <c r="D80" s="4">
-        <v>55.95073</v>
+        <v>55.950769999999999</v>
       </c>
       <c r="E80" s="4">
-        <v>-3.1614900000000001</v>
+        <v>-3.1614200000000001</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J80" s="4">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="K80" s="4">
         <v>11</v>
       </c>
       <c r="L80" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M80" s="4">
+        <v>58</v>
+      </c>
+      <c r="N80" s="4">
         <v>57</v>
       </c>
-      <c r="N80" s="4">
-        <v>19</v>
-      </c>
       <c r="O80" s="4">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>18</v>
@@ -4417,45 +4411,45 @@
         <v>26</v>
       </c>
       <c r="D81" s="4">
-        <v>55.950769999999999</v>
+        <v>55.950719999999997</v>
       </c>
       <c r="E81" s="4">
-        <v>-3.1614200000000001</v>
+        <v>-3.1610200000000002</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J81" s="4">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="K81" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L81" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M81" s="4">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="N81" s="4">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O81" s="4">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>18</v>
@@ -4464,45 +4458,45 @@
         <v>26</v>
       </c>
       <c r="D82" s="4">
-        <v>55.950719999999997</v>
+        <v>55.950490000000002</v>
       </c>
       <c r="E82" s="4">
-        <v>-3.1610200000000002</v>
+        <v>-3.1610900000000002</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J82" s="4">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="K82" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L82" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M82" s="4">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="N82" s="4">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="O82" s="4">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>18</v>
@@ -4511,139 +4505,139 @@
         <v>26</v>
       </c>
       <c r="D83" s="4">
-        <v>55.950510000000001</v>
+        <v>55.950479999999999</v>
       </c>
       <c r="E83" s="4">
-        <v>-3.1610800000000001</v>
+        <v>-3.16107</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J83" s="4">
-        <v>346</v>
+        <v>67</v>
       </c>
       <c r="K83" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L83" s="4">
         <v>0</v>
       </c>
       <c r="M83" s="4">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="N83" s="4">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="O83" s="4">
-        <v>117</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D84" s="4">
-        <v>55.950490000000002</v>
+      <c r="D84" s="8">
+        <v>55.925690000000003</v>
       </c>
       <c r="E84" s="4">
-        <v>-3.1610900000000002</v>
+        <v>-3.1920799999999998</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J84" s="4">
-        <v>207</v>
+        <v>750</v>
       </c>
       <c r="K84" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L84" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M84" s="4">
-        <v>91</v>
+        <v>522</v>
       </c>
       <c r="N84" s="4">
-        <v>116</v>
+        <v>228</v>
       </c>
       <c r="O84" s="4">
-        <v>41</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="4">
-        <v>55.950479999999999</v>
+      <c r="D85" s="8">
+        <v>55.925539999999998</v>
       </c>
       <c r="E85" s="4">
-        <v>-3.16107</v>
+        <v>-3.1924000000000001</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J85" s="4">
-        <v>67</v>
+        <v>525</v>
       </c>
       <c r="K85" s="4">
+        <v>3</v>
+      </c>
+      <c r="L85" s="4">
         <v>2</v>
       </c>
-      <c r="L85" s="4">
-        <v>0</v>
-      </c>
       <c r="M85" s="4">
-        <v>45</v>
+        <v>454</v>
       </c>
       <c r="N85" s="4">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="O85" s="4">
-        <v>22</v>
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>11</v>
@@ -4652,45 +4646,45 @@
         <v>26</v>
       </c>
       <c r="D86" s="8">
-        <v>55.925690000000003</v>
+        <v>55.925409999999999</v>
       </c>
       <c r="E86" s="4">
-        <v>-3.1920799999999998</v>
+        <v>-3.1927300000000001</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J86" s="4">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="K86" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L86" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M86" s="4">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="N86" s="4">
+        <v>324</v>
+      </c>
+      <c r="O86" s="4">
         <v>228</v>
-      </c>
-      <c r="O86" s="4">
-        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>11</v>
@@ -4699,45 +4693,45 @@
         <v>26</v>
       </c>
       <c r="D87" s="8">
-        <v>55.925539999999998</v>
+        <v>55.92559</v>
       </c>
       <c r="E87" s="4">
-        <v>-3.1924000000000001</v>
+        <v>-3.19286</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J87" s="4">
-        <v>525</v>
+        <v>892</v>
       </c>
       <c r="K87" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L87" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M87" s="4">
-        <v>454</v>
+        <v>619</v>
       </c>
       <c r="N87" s="4">
-        <v>71</v>
+        <v>273</v>
       </c>
       <c r="O87" s="4">
-        <v>293</v>
+        <v>274</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>11</v>
@@ -4746,45 +4740,45 @@
         <v>26</v>
       </c>
       <c r="D88" s="8">
-        <v>55.925409999999999</v>
+        <v>55.925150000000002</v>
       </c>
       <c r="E88" s="4">
-        <v>-3.1927300000000001</v>
+        <v>-3.1938900000000001</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J88" s="4">
-        <v>825</v>
+        <v>515</v>
       </c>
       <c r="K88" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L88" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M88" s="4">
-        <v>501</v>
+        <v>318</v>
       </c>
       <c r="N88" s="4">
-        <v>324</v>
+        <v>197</v>
       </c>
       <c r="O88" s="4">
-        <v>228</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>11</v>
@@ -4793,45 +4787,45 @@
         <v>26</v>
       </c>
       <c r="D89" s="8">
-        <v>55.92559</v>
+        <v>55.925330000000002</v>
       </c>
       <c r="E89" s="4">
-        <v>-3.19286</v>
+        <v>-3.1939700000000002</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="J89" s="4">
-        <v>892</v>
+        <v>838</v>
       </c>
       <c r="K89" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L89" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M89" s="4">
-        <v>619</v>
+        <v>559</v>
       </c>
       <c r="N89" s="4">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O89" s="4">
-        <v>274</v>
+        <v>243</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>11</v>
@@ -4840,45 +4834,45 @@
         <v>26</v>
       </c>
       <c r="D90" s="8">
-        <v>55.925150000000002</v>
-      </c>
-      <c r="E90" s="4">
-        <v>-3.1938900000000001</v>
+        <v>55.925469999999997</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-3.1909900000000002</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J90" s="4">
-        <v>515</v>
+        <v>441</v>
       </c>
       <c r="K90" s="4">
         <v>2</v>
       </c>
       <c r="L90" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="4">
-        <v>318</v>
+        <v>404</v>
       </c>
       <c r="N90" s="4">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="O90" s="4">
-        <v>266</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>11</v>
@@ -4887,45 +4881,45 @@
         <v>26</v>
       </c>
       <c r="D91" s="8">
-        <v>55.925330000000002</v>
+        <v>55.92539</v>
       </c>
       <c r="E91" s="4">
-        <v>-3.1939700000000002</v>
+        <v>-3.1910500000000002</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I91" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J91" s="4">
-        <v>838</v>
+        <v>694</v>
       </c>
       <c r="K91" s="4">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L91" s="4">
         <v>0</v>
       </c>
       <c r="M91" s="4">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N91" s="4">
-        <v>279</v>
+        <v>139</v>
       </c>
       <c r="O91" s="4">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>11</v>
@@ -4934,45 +4928,45 @@
         <v>26</v>
       </c>
       <c r="D92" s="8">
-        <v>55.925469999999997</v>
+        <v>55.925429999999999</v>
       </c>
       <c r="E92" s="8">
-        <v>-3.1909900000000002</v>
+        <v>-3.1912400000000001</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J92" s="4">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="K92" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L92" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M92" s="4">
-        <v>404</v>
+        <v>262</v>
       </c>
       <c r="N92" s="4">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="O92" s="4">
-        <v>179</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>11</v>
@@ -4981,139 +4975,139 @@
         <v>26</v>
       </c>
       <c r="D93" s="8">
-        <v>55.92539</v>
-      </c>
-      <c r="E93" s="4">
-        <v>-3.1910500000000002</v>
+        <v>55.925609999999999</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-3.1913999999999998</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J93" s="4">
-        <v>694</v>
+        <v>836</v>
       </c>
       <c r="K93" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L93" s="4">
         <v>0</v>
       </c>
       <c r="M93" s="4">
-        <v>555</v>
+        <v>632</v>
       </c>
       <c r="N93" s="4">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="O93" s="4">
-        <v>252</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D94" s="8">
-        <v>55.925429999999999</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-3.1912400000000001</v>
+        <v>29</v>
+      </c>
+      <c r="D94" s="4">
+        <v>55.95682</v>
+      </c>
+      <c r="E94" s="4">
+        <v>-3.2772999999999999</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J94" s="4">
-        <v>391</v>
+        <v>740</v>
       </c>
       <c r="K94" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L94" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M94" s="4">
-        <v>262</v>
+        <v>370</v>
       </c>
       <c r="N94" s="4">
-        <v>129</v>
+        <v>370</v>
       </c>
       <c r="O94" s="4">
-        <v>54</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D95" s="8">
-        <v>55.925609999999999</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-3.1913999999999998</v>
+        <v>29</v>
+      </c>
+      <c r="D95" s="4">
+        <v>55.956879999999998</v>
+      </c>
+      <c r="E95" s="4">
+        <v>-3.2774399999999999</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="J95" s="4">
-        <v>836</v>
+        <v>145</v>
       </c>
       <c r="K95" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L95" s="4">
         <v>0</v>
       </c>
       <c r="M95" s="4">
-        <v>632</v>
+        <v>85</v>
       </c>
       <c r="N95" s="4">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="O95" s="4">
-        <v>197</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>23</v>
@@ -5122,45 +5116,45 @@
         <v>29</v>
       </c>
       <c r="D96" s="4">
-        <v>55.95682</v>
+        <v>55.956859999999999</v>
       </c>
       <c r="E96" s="4">
-        <v>-3.2772999999999999</v>
+        <v>-3.27739</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J96" s="4">
-        <v>740</v>
+        <v>865</v>
       </c>
       <c r="K96" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L96" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M96" s="4">
-        <v>370</v>
+        <v>495</v>
       </c>
       <c r="N96" s="4">
         <v>370</v>
       </c>
       <c r="O96" s="4">
-        <v>260</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>23</v>
@@ -5169,45 +5163,45 @@
         <v>29</v>
       </c>
       <c r="D97" s="4">
-        <v>55.956879999999998</v>
+        <v>55.957630000000002</v>
       </c>
       <c r="E97" s="4">
-        <v>-3.2774399999999999</v>
+        <v>-3.2770000000000001</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="J97" s="4">
-        <v>145</v>
+        <v>740</v>
       </c>
       <c r="K97" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L97" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M97" s="4">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="N97" s="4">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="O97" s="4">
-        <v>85</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>23</v>
@@ -5216,45 +5210,45 @@
         <v>29</v>
       </c>
       <c r="D98" s="4">
-        <v>55.956859999999999</v>
+        <v>55.957320000000003</v>
       </c>
       <c r="E98" s="4">
-        <v>-3.27739</v>
+        <v>-3.2762600000000002</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J98" s="4">
-        <v>865</v>
+        <v>1280</v>
       </c>
       <c r="K98" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L98" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M98" s="4">
-        <v>495</v>
+        <v>750</v>
       </c>
       <c r="N98" s="4">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="O98" s="4">
-        <v>220</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>23</v>
@@ -5263,45 +5257,45 @@
         <v>29</v>
       </c>
       <c r="D99" s="4">
-        <v>55.957630000000002</v>
+        <v>55.957430000000002</v>
       </c>
       <c r="E99" s="4">
-        <v>-3.2770000000000001</v>
+        <v>-3.2574299999999998</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J99" s="4">
-        <v>740</v>
+        <v>875</v>
       </c>
       <c r="K99" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L99" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M99" s="4">
-        <v>460</v>
+        <v>675</v>
       </c>
       <c r="N99" s="4">
+        <v>200</v>
+      </c>
+      <c r="O99" s="4">
         <v>280</v>
-      </c>
-      <c r="O99" s="4">
-        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>23</v>
@@ -5310,45 +5304,45 @@
         <v>29</v>
       </c>
       <c r="D100" s="4">
-        <v>55.957320000000003</v>
+        <v>55.957369999999997</v>
       </c>
       <c r="E100" s="4">
-        <v>-3.2762600000000002</v>
+        <v>-3.2764000000000002</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J100" s="4">
-        <v>1280</v>
+        <v>735</v>
       </c>
       <c r="K100" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L100" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M100" s="4">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="N100" s="4">
-        <v>530</v>
+        <v>235</v>
       </c>
       <c r="O100" s="4">
-        <v>320</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>23</v>
@@ -5357,45 +5351,45 @@
         <v>29</v>
       </c>
       <c r="D101" s="4">
-        <v>55.957430000000002</v>
+        <v>55.957360000000001</v>
       </c>
       <c r="E101" s="4">
-        <v>-3.2574299999999998</v>
+        <v>-3.2763599999999999</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I101" s="4" t="s">
-        <v>44</v>
+      <c r="I101" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="J101" s="4">
-        <v>875</v>
+        <v>767</v>
       </c>
       <c r="K101" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L101" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M101" s="4">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="N101" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O101" s="4">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>23</v>
@@ -5404,45 +5398,45 @@
         <v>29</v>
       </c>
       <c r="D102" s="4">
-        <v>55.957369999999997</v>
+        <v>55.956510000000002</v>
       </c>
       <c r="E102" s="4">
-        <v>-3.2764000000000002</v>
+        <v>-3.2758500000000002</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J102" s="4">
-        <v>735</v>
+        <v>1333</v>
       </c>
       <c r="K102" s="4">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="L102" s="4">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="M102" s="4">
-        <v>500</v>
+        <v>1033</v>
       </c>
       <c r="N102" s="4">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="O102" s="4">
-        <v>177</v>
+        <v>320</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>23</v>
@@ -5451,45 +5445,45 @@
         <v>29</v>
       </c>
       <c r="D103" s="4">
-        <v>55.957360000000001</v>
+        <v>55.956659999999999</v>
       </c>
       <c r="E103" s="4">
-        <v>-3.2763599999999999</v>
+        <v>-3.2759</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I103" s="9" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J103" s="4">
-        <v>767</v>
+        <v>590</v>
       </c>
       <c r="K103" s="4">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="L103" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M103" s="4">
-        <v>667</v>
+        <v>420</v>
       </c>
       <c r="N103" s="4">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="O103" s="4">
-        <v>320</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>23</v>
@@ -5498,45 +5492,45 @@
         <v>29</v>
       </c>
       <c r="D104" s="4">
-        <v>55.956510000000002</v>
+        <v>55.953389999999999</v>
       </c>
       <c r="E104" s="4">
-        <v>-3.2758500000000002</v>
+        <v>-3.2753700000000001</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J104" s="4">
-        <v>1333</v>
+        <v>129</v>
       </c>
       <c r="K104" s="4">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L104" s="4">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="M104" s="4">
-        <v>1033</v>
+        <v>96</v>
       </c>
       <c r="N104" s="4">
-        <v>300</v>
+        <v>33</v>
       </c>
       <c r="O104" s="4">
-        <v>320</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>23</v>
@@ -5545,45 +5539,45 @@
         <v>29</v>
       </c>
       <c r="D105" s="4">
-        <v>55.956659999999999</v>
+        <v>55.951650000000001</v>
       </c>
       <c r="E105" s="4">
-        <v>-3.2759</v>
+        <v>-3.2737099999999999</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J105" s="4">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="K105" s="4">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L105" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M105" s="4">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="N105" s="4">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="O105" s="4">
-        <v>140</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>23</v>
@@ -5592,45 +5586,45 @@
         <v>29</v>
       </c>
       <c r="D106" s="4">
-        <v>55.953389999999999</v>
+        <v>55.951309999999999</v>
       </c>
       <c r="E106" s="4">
-        <v>-3.2753700000000001</v>
+        <v>-3.27366</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>50</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J106" s="4">
-        <v>129</v>
+        <v>720</v>
       </c>
       <c r="K106" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L106" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M106" s="4">
-        <v>96</v>
+        <v>410</v>
       </c>
       <c r="N106" s="4">
-        <v>33</v>
+        <v>310</v>
       </c>
       <c r="O106" s="4">
-        <v>17</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>23</v>
@@ -5639,63 +5633,63 @@
         <v>29</v>
       </c>
       <c r="D107" s="4">
-        <v>55.951650000000001</v>
+        <v>55.951250000000002</v>
       </c>
       <c r="E107" s="4">
-        <v>-3.2737099999999999</v>
+        <v>-3.2738</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J107" s="4">
-        <v>615</v>
+        <v>880</v>
       </c>
       <c r="K107" s="4">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="L107" s="4">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="M107" s="4">
-        <v>365</v>
+        <v>630</v>
       </c>
       <c r="N107" s="4">
         <v>250</v>
       </c>
       <c r="O107" s="4">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D108" s="4">
-        <v>55.951309999999999</v>
+        <v>55.940809999999999</v>
       </c>
       <c r="E108" s="4">
-        <v>-3.27366</v>
+        <v>-3.1642000000000001</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>52</v>
@@ -5704,74 +5698,74 @@
         <v>44</v>
       </c>
       <c r="J108" s="4">
-        <v>720</v>
+        <v>21</v>
       </c>
       <c r="K108" s="4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L108" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M108" s="4">
-        <v>410</v>
+        <v>13</v>
       </c>
       <c r="N108" s="4">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="O108" s="4">
-        <v>190</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D109" s="4">
-        <v>55.951250000000002</v>
+        <v>55.940840000000001</v>
       </c>
       <c r="E109" s="4">
-        <v>-3.2738</v>
+        <v>-3.1640199999999998</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>52</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J109" s="4">
-        <v>880</v>
+        <v>30</v>
       </c>
       <c r="K109" s="4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L109" s="4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M109" s="4">
-        <v>630</v>
+        <v>15</v>
       </c>
       <c r="N109" s="4">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="O109" s="4">
-        <v>230</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>8</v>
@@ -5780,45 +5774,45 @@
         <v>26</v>
       </c>
       <c r="D110" s="4">
-        <v>55.940809999999999</v>
+        <v>55.940660000000001</v>
       </c>
       <c r="E110" s="4">
-        <v>-3.1642000000000001</v>
+        <v>-3.1640199999999998</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J110" s="4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K110" s="4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L110" s="4">
         <v>0</v>
       </c>
       <c r="M110" s="4">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N110" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O110" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>8</v>
@@ -5827,45 +5821,45 @@
         <v>26</v>
       </c>
       <c r="D111" s="4">
-        <v>55.940840000000001</v>
+        <v>55.940689999999996</v>
       </c>
       <c r="E111" s="4">
-        <v>-3.1640199999999998</v>
+        <v>-3.16398</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I111" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="J111" s="4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K111" s="4">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L111" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="4">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="N111" s="4">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="O111" s="4">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>8</v>
@@ -5874,45 +5868,45 @@
         <v>26</v>
       </c>
       <c r="D112" s="4">
-        <v>55.940660000000001</v>
+        <v>55.9405</v>
       </c>
       <c r="E112" s="4">
-        <v>-3.1640199999999998</v>
+        <v>-3.16276</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I112" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="J112" s="4">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K112" s="4">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L112" s="4">
         <v>0</v>
       </c>
       <c r="M112" s="4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="N112" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O112" s="4">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>8</v>
@@ -5921,45 +5915,45 @@
         <v>26</v>
       </c>
       <c r="D113" s="4">
-        <v>55.940689999999996</v>
+        <v>55.940469999999998</v>
       </c>
       <c r="E113" s="4">
-        <v>-3.16398</v>
+        <v>-3.1625299999999998</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J113" s="4">
+        <v>16</v>
+      </c>
+      <c r="K113" s="4">
+        <v>14</v>
+      </c>
+      <c r="L113" s="4">
         <v>8</v>
       </c>
-      <c r="K113" s="4">
-        <v>18</v>
-      </c>
-      <c r="L113" s="4">
-        <v>1</v>
-      </c>
       <c r="M113" s="4">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="N113" s="4">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="O113" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>8</v>
@@ -5968,10 +5962,10 @@
         <v>26</v>
       </c>
       <c r="D114" s="4">
-        <v>55.9405</v>
+        <v>55.940379999999998</v>
       </c>
       <c r="E114" s="4">
-        <v>-3.16276</v>
+        <v>-3.1599599999999999</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>31</v>
@@ -5980,121 +5974,27 @@
         <v>10</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I114" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="I114" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="J114" s="4">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="K114" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L114" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M114" s="4">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="N114" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O114" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A115" s="4">
-        <v>114</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D115" s="4">
-        <v>55.940469999999998</v>
-      </c>
-      <c r="E115" s="4">
-        <v>-3.1625299999999998</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J115" s="4">
-        <v>16</v>
-      </c>
-      <c r="K115" s="4">
-        <v>14</v>
-      </c>
-      <c r="L115" s="4">
-        <v>8</v>
-      </c>
-      <c r="M115" s="4">
-        <v>11</v>
-      </c>
-      <c r="N115" s="4">
-        <v>5</v>
-      </c>
-      <c r="O115" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A116" s="4">
-        <v>115</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D116" s="4">
-        <v>55.940379999999998</v>
-      </c>
-      <c r="E116" s="4">
-        <v>-3.1599599999999999</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I116" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J116" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="K116" s="4">
-        <v>12</v>
-      </c>
-      <c r="L116" s="4">
-        <v>12</v>
-      </c>
-      <c r="M116" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="N116" s="4">
-        <v>2</v>
-      </c>
-      <c r="O116" s="4">
         <v>3.5</v>
       </c>
     </row>
